--- a/鑄件盤點資料.xlsx
+++ b/鑄件盤點資料.xlsx
@@ -10988,7 +10988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11078,7 +11078,7 @@
         </is>
       </c>
       <c r="C2" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="53" t="n">
         <v>0</v>
@@ -11091,7 +11091,7 @@
       </c>
       <c r="G2" s="53" t="inlineStr"/>
       <c r="H2" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" s="53" t="inlineStr"/>
       <c r="J2" s="53" t="inlineStr"/>
@@ -11784,10 +11784,10 @@
         <v>1</v>
       </c>
       <c r="D23" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="53" t="n">
         <v>0</v>
@@ -11857,13 +11857,13 @@
         </is>
       </c>
       <c r="C25" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="D25" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="F25" s="53" t="n">
         <v>0</v>
@@ -11964,7 +11964,7 @@
         </is>
       </c>
       <c r="C28" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" s="53" t="n">
         <v>0</v>
@@ -11976,7 +11976,9 @@
         <v>0</v>
       </c>
       <c r="G28" s="53" t="inlineStr"/>
-      <c r="H28" s="53" t="inlineStr"/>
+      <c r="H28" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="I28" s="53" t="inlineStr"/>
       <c r="J28" s="53" t="inlineStr"/>
       <c r="K28" s="53" t="inlineStr"/>
@@ -12550,7 +12552,7 @@
         </is>
       </c>
       <c r="C46" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="53" t="n">
         <v>0</v>
@@ -12562,7 +12564,9 @@
         <v>0</v>
       </c>
       <c r="G46" s="53" t="inlineStr"/>
-      <c r="H46" s="53" t="inlineStr"/>
+      <c r="H46" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="I46" s="53" t="inlineStr"/>
       <c r="J46" s="53" t="n">
         <v>0</v>
@@ -12585,7 +12589,7 @@
         </is>
       </c>
       <c r="C47" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" s="53" t="n">
         <v>0</v>
@@ -12597,7 +12601,9 @@
         <v>0</v>
       </c>
       <c r="G47" s="53" t="inlineStr"/>
-      <c r="H47" s="53" t="inlineStr"/>
+      <c r="H47" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="I47" s="53" t="inlineStr"/>
       <c r="J47" s="53" t="inlineStr"/>
       <c r="K47" s="53" t="n">
@@ -12658,10 +12664,12 @@
         <v>1</v>
       </c>
       <c r="F49" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="53" t="inlineStr"/>
+      <c r="H49" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G49" s="53" t="inlineStr"/>
-      <c r="H49" s="53" t="inlineStr"/>
       <c r="I49" s="53" t="inlineStr"/>
       <c r="J49" s="53" t="n">
         <v>0</v>
@@ -13047,19 +13055,21 @@
         </is>
       </c>
       <c r="C61" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="53" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F61" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="53" t="inlineStr"/>
-      <c r="H61" s="53" t="inlineStr"/>
+      <c r="H61" s="53" t="n">
+        <v>3</v>
+      </c>
       <c r="I61" s="53" t="inlineStr"/>
       <c r="J61" s="53" t="inlineStr"/>
       <c r="K61" s="53" t="inlineStr"/>
@@ -13109,19 +13119,21 @@
         </is>
       </c>
       <c r="C63" s="53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63" s="53" t="n">
         <v>0</v>
       </c>
       <c r="E63" s="53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F63" s="53" t="n">
         <v>0</v>
       </c>
       <c r="G63" s="53" t="inlineStr"/>
-      <c r="H63" s="53" t="inlineStr"/>
+      <c r="H63" s="53" t="n">
+        <v>2</v>
+      </c>
       <c r="I63" s="53" t="inlineStr"/>
       <c r="J63" s="53" t="inlineStr"/>
       <c r="K63" s="53" t="inlineStr"/>
@@ -13295,7 +13307,7 @@
         </is>
       </c>
       <c r="C69" s="53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D69" s="53" t="n">
         <v>0</v>
@@ -13304,10 +13316,12 @@
         <v>0</v>
       </c>
       <c r="F69" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" s="53" t="inlineStr"/>
-      <c r="H69" s="53" t="inlineStr"/>
+      <c r="H69" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="I69" s="53" t="inlineStr"/>
       <c r="J69" s="53" t="n">
         <v>0</v>
@@ -13354,37 +13368,6 @@
       </c>
       <c r="N70" s="53" t="inlineStr"/>
       <c r="O70" s="53" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="53" t="n">
-        <v>8810001522</v>
-      </c>
-      <c r="B71" s="53" t="inlineStr">
-        <is>
-          <t>TGV-106底座</t>
-        </is>
-      </c>
-      <c r="C71" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="53" t="inlineStr"/>
-      <c r="H71" s="53" t="inlineStr"/>
-      <c r="I71" s="53" t="inlineStr"/>
-      <c r="J71" s="53" t="inlineStr"/>
-      <c r="K71" s="53" t="inlineStr"/>
-      <c r="L71" s="53" t="inlineStr"/>
-      <c r="M71" s="53" t="inlineStr"/>
-      <c r="N71" s="53" t="inlineStr"/>
-      <c r="O71" s="53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13497,7 +13480,7 @@
         </is>
       </c>
       <c r="C2" s="53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2" s="53" t="n">
         <v>0</v>
@@ -13516,7 +13499,7 @@
       </c>
       <c r="I2" s="53" t="inlineStr"/>
       <c r="J2" s="53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" s="53" t="inlineStr"/>
       <c r="L2" s="53" t="inlineStr"/>
@@ -13612,7 +13595,7 @@
         </is>
       </c>
       <c r="C5" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D5" s="53" t="n">
         <v>0</v>
@@ -13631,7 +13614,7 @@
       </c>
       <c r="I5" s="53" t="inlineStr"/>
       <c r="J5" s="53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" s="53" t="inlineStr"/>
       <c r="L5" s="53" t="n">
@@ -13908,7 +13891,7 @@
         </is>
       </c>
       <c r="C13" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="53" t="n">
         <v>0</v>
@@ -13927,7 +13910,7 @@
       </c>
       <c r="I13" s="53" t="inlineStr"/>
       <c r="J13" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K13" s="53" t="inlineStr"/>
       <c r="L13" s="53" t="n">
@@ -14038,11 +14021,11 @@
         <v>0</v>
       </c>
       <c r="H16" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" s="53" t="inlineStr"/>
       <c r="J16" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K16" s="53" t="inlineStr"/>
       <c r="L16" s="53" t="inlineStr"/>
@@ -14317,15 +14300,19 @@
       <c r="E24" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="53" t="inlineStr"/>
+      <c r="F24" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="G24" s="53" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I24" s="53" t="inlineStr"/>
-      <c r="J24" s="53" t="inlineStr"/>
+      <c r="J24" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" s="53" t="inlineStr"/>
       <c r="L24" s="53" t="inlineStr"/>
       <c r="M24" s="53" t="inlineStr"/>
@@ -14426,17 +14413,21 @@
         <v>0</v>
       </c>
       <c r="E27" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F27" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="G27" s="53" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" s="53" t="inlineStr"/>
-      <c r="J27" s="53" t="inlineStr"/>
+      <c r="J27" s="53" t="n">
+        <v>4</v>
+      </c>
       <c r="K27" s="53" t="inlineStr"/>
       <c r="L27" s="53" t="n">
         <v>0</v>
@@ -14651,23 +14642,23 @@
         <v>0</v>
       </c>
       <c r="D33" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="E33" s="53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="I33" s="53" t="inlineStr"/>
       <c r="J33" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" s="53" t="inlineStr"/>
       <c r="L33" s="53" t="inlineStr"/>
@@ -14766,12 +14757,14 @@
         <v>0</v>
       </c>
       <c r="D36" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="53" t="inlineStr"/>
+      <c r="F36" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="G36" s="53" t="n">
         <v>0</v>
       </c>
@@ -14779,7 +14772,9 @@
         <v>0</v>
       </c>
       <c r="I36" s="53" t="inlineStr"/>
-      <c r="J36" s="53" t="inlineStr"/>
+      <c r="J36" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" s="53" t="inlineStr"/>
       <c r="L36" s="53" t="n">
         <v>0</v>
@@ -14846,7 +14841,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E38" s="53" t="n">
         <v>0</v>
@@ -14862,7 +14857,7 @@
       </c>
       <c r="I38" s="53" t="inlineStr"/>
       <c r="J38" s="53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K38" s="53" t="inlineStr"/>
       <c r="L38" s="53" t="inlineStr"/>

--- a/鑄件盤點資料.xlsx
+++ b/鑄件盤點資料.xlsx
@@ -1124,2601 +1124,6 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>guang</author>
-    <author>hsinwei</author>
-    <author>ralf</author>
-    <author>001289</author>
-  </authors>
-  <commentList>
-    <comment ref="F2" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-3/2 M5*1 OK</t>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-7/27 出1台(三廠)
-</t>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-1/7 M6*1 OK(17M)
-10/22 M6*1 OK(17M)
-10/27 M6*1 OK(17M)
-</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/19 入1台(YZ)(NEW)
-3/30 入1台(YZ)(NEW)
-4/11 入1台(YZ)(NEW)
-</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/30 M6*1 OK(17M)
-5/2 M6*1 OK(17M)
-25/5/27 M6*1 OK(17M)
-</t>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-7/20 M5*1 OK(813)
-7/24 M5*1 OK(813)
-7/24 出1台(轉台典研-HA18072002)
-8/2 出1台(轉台典研-HA18072402)
-25/6/6 M5*1 OK(813)(000400005768)
-</t>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="1" shapeId="0">
-      <text>
-        <t xml:space="preserve">hsinwei:
-25/06/23 ok
-06/24出三廠(HA25060601-000400005768-100003301)
-</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-12/12 4支送傑晃加工guang:
-5/10 入2台(YZ)
-7/11 入1台(YZ-換)
-</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-NG品*1guang:
-5/30 M6*1 OK(410)
-5/31 M6*1 OK(410)
-long:
-7/26 m6*1 ok(523)
-guang:
-12/22 出1台(報廢)
-</t>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/13台偉入6台
-3/13台偉入4台
-4/17 入 6支(傑晃)
-5/12 台偉入6台
-7/10 台偉入4台
-guang:
-6/5 M5*1 OK(410)
-6/6 M5*1 OK(410)
-7/29 M5*1 OK(523)
-</t>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-3/24 出4支
-3/28 出1支
-4/18 出1支(本廠)
-5/3  出1台(本廠)
-5/15  出5台(本廠)
-5/17  出1台(本廠)
-6/01  出2台(本廠)
-6/12  出2台(本廠)
-6/14  出1台(本廠)
-6/28  出3台(本廠)
-7/20  出1台(本廠)
-8/2  出3台(本廠)
-8/21  出1台(本廠)
-6/28 研*2 OK
-6/28  出1台(本廠-HA19060402)
-7/12  出1台(本廠-HA19060601)
-8/5 研*1 OK
-8/5  出1台(本廠-HA19073002)
-</t>
-      </text>
-    </comment>
-    <comment ref="C6" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/7 入2台(YZ)
-4/17 入1台(YZ)
-5/22 入1台(YZ)(新板)
-6/5 入2台(YZ)(新板)
-7/19 入1台(YZ)(新板)
-9/6 入1台(YZ)(新板)
-9/14 入1台(YZ)(新板)
-9/26入1台(YZ)(新板)
-10/16入1台(YZ)(新板)
-10/26入1台(YZ)(新板)
-10/27 入1台(YZ)(新板)
-1/4 入1台(YZ)(新板)
-1/15 入1台(YZ)(NEW)
-3/1 入1台(YZ)(NEW)
-3/5 入2台(YZ)(NEW)
-3/12 入2台(YZ)(NEW)
-5/14 入2台(YZ)(NEW)
-5/16 入1台(YZ)(NEW)
-6/8 入2台(YZ)(NEW)
-7/11 入2台(YZ)(NEW)
-7/20 入1台(YZ)(NEW)
-7/30 入1台(YZ)(NEW)
-11/22 入2台(YZ)(NEW)
-11/28 入2台(YZ)(NEW)
-3/6 入2台(YZ)(NEW)
-3/11 入1台(YZ)(NEW)
-6/17 入2台(YZ)(NEW)
-21/6/28 入1台(YZ)(NEW)
-22/6/21 入2台(YZ-#2820-#2874)
-6/24 入1台(LD-#2897)
-hsinwei:
-25/10/7 入1台(LD-#5984)
-</t>
-      </text>
-    </comment>
-    <comment ref="E6" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-4/24 M6*1OK(17米)
-5/27 M6*1OK(17米)(新)
-6/19 M6*1OK(17米)(新)
-6/20 M6*1OK(17m)(新
-7/21M6*1OK(17M)(新
-9/11M6*1OK(17M)(新
-9/20M6*1OK(17M)(新
-10/2M6*1OK(17M)(新
-10/25M6*1OK(17M)(新)
-10/26M6*1OK(17M)(新)
-11/1M6*1OK(17M)(新)
-11/2 M6*1OK(17M)(新)
-11/13 M6*1OK(17M)(新)
-2/12 M6*1OK(17M)(新)
-2/13 M6*2 OK(17M)(新)
-3/28 M6*1 OK(17M)(新)
-3/29 M6*1 OK(17M)(新)
-4/11 M6*1 OK(17M)(新)
-4/12 M6*1 OK(17M)(新)
-4/25 M6*1 OK(17M)(新)
-5/22 M6*1 OK(17M)(新)
-6/5 M6*1 OK(17M)(新)
-6/6 M6*1 OK(17M)(新)
-long:
-6/21 M6*1 OK(17M新)
-6/22 M6*1 OK(17M新)
-9/19 M6*1 OK(17M)(新)
-9/20 M6*1 OK(17M)(新)
-10/11 M6*1 OK(17M)(新)
-11/8 M6*1 OK(17M)(新)
-11/9 M6*1 OK(17M)(新)
-1/2 M6*1 OK(17M)(新)
-1/3 M6*1 OK(17M)(新)
-1/4 M6*1 OK(17M)(新)
-1/5 M6*1 OK(17M)(新)
-8/18 M6*1 OK(17M)(新)
-8/21 M6*1 OK(17M)(新)
-8/25 M6*1 OK(17M)(新)
-21/6/29 M6*1 OK(17M)(新)
-6/30 M6*1 OK(17M)(新)
-8/9 M6*1 OK(17M)
-8/10 M6*1 OK(17M)
-22/6/29 M6*1 OK(17M-#2820)
-7/1 M6*1 OK(17M-#2874)
-7/4 M6*1 OK(17M-#2897)
-guang:
-25/10/13 M6*1 OK(17M-#5984)
-</t>
-      </text>
-    </comment>
-    <comment ref="F6" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">
-guang:
-6/3 M5*1 OK(410)
-6/27 M5*1 OK(410)
-6/29 M5*1 OK(410)
-7/27 M5*1 OK(409)
-9/13 M5*1 OK(409)
-9/22 M5*1 OK(409)
-10/12 M5*1 OK(409)
-11/1 M5*1 OK(409)
-11/27 M5*1 OK(409)
-12/27 M5*1 OK(409)
-12/28 M5*1 OK(409)
-1/02 M5*1 OK(409)
-2/27 M5*1 OK(409)
-3/13 M5*1 OK(409)
-3/24 M5*1 OK(409)
-4/9 M5*1 OK(409)
-4/11 M5*1 OK(409)
-4/24 M5*1 OK(409)
-4/25 M5*1 OK(409)
-4/27 M5*1 OK(409)
-6/4 M5*1 OK(409)
-long:
-6/19 M5*1 OK(409)
-6/21 M5*1 OK(409)
-6/27 M5*1 OK(409)
-6/29 M5*1 OK(409)
-9/27 M5*1 OK(409)
-10/1 M5*1 OK(409)
-10/19 M5*1 OK(409)
-11/19 M5*1 OK(409)
-11/22 M5*1 OK(409)
-2/20 M5*1 OK(409)
-2/22 M5*1 OK(409)
-2/26 M5*1 OK(409)
-3/5 M5*1 OK(409)
-21/3/17 M5*1 OK(410-H08000807)
-3/24 M5*1 OK(410-H08000807)
-3/30 M5*1 OK(410-H08000808-#2897)
-7/13 M5*1 OK(410-000400001077)
-7/16 M5*1 OK(410-000400001077)
-8/17 M5*1 OK(410-000400001158)
-8/20 M5*1 OK(410-000400001158)
-22/8/20 M5*1 OK(410-000400002874)
-8/25 M5*1 OK(410-000400002820)
-8/29 M5*1 OK(410-#2897-H08000808)
-25/10/22 M5*1 OK(410-000400005984)
-guang:
-guang:
-hsinwei:
-</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-1/23 出1台(3廠)
-2/7 出1台(3廠)
-2/8 出1台(本廠)
-3/21 出1台(本廠)
-4/18 出1台(本廠)
-5/29 出1台(3廠)
-6/4 出1台(本廠)
-6/8 出1台(本廠)
-6/19 出1台(3廠)
-7/25 出2台(本廠)
-8/23 出1台(本廠)
-9/27 出1台(3廠)
-10/23 研*1 OK
-10/25 研*1 OK
-10/29 研*1 OK
-11/6 研*1 OK
-11/12 出1台(6路)
-11/19 出2台(6路)
-1/25 出1台(6路-HA18062901)
-1/31 研*1 OK
-2/12 研*1 OK
-1/25 出2台(6路-HA18111901,HA18092901)
-7/31 研*1 OK
-11/5 研*1 OK
-12/4 研*1 OK
-5/5 研*1 OK
-12/11 出1台(6路-HA19022202-26787)
-21/2/5 出1台(6路-HA19022002-100000248)
-3/4 出1台(6路-HA19022601-100000216)
-3/23 出1台(6路-HA18112201-100000425)
-3/24 出1台(3廠-HA18120602-100000298)
-4/9 出1台(3廠-HA18060401-100000485)
-4/14 研*1 OK
-4/15 研*1 OK
-5/6 出1台(6路-HA21031701-100000395-H08000807)
-5/6 出1台(6路-HA21032301-100000396-H08000807)
-5/22 研*1 OK(H08000808)
-8/5 研*1 OK(000400001077)
-11/25 研*2 OK(000400001158)
-22/3/29 出1台(3廠-HA21082001-100001656-000400001158)
-4/25 出1台(3廠-HA21071301-100001436-000400001077)
-guang:
-5/11 出1台(3廠-HA21071601-100001437-000400001077)
-9/8 研*1 OK(000400002820)
-001289:
-10/14 研*1 OK(000400002897)
-001289:
-23/5/2 出1台(3廠-HA22082501-100002321-000400002820)
-6/27 研*1 OK(000400002874)
-10/16 出1台(3廠-HA22082001-100002504-000400002874)
-guang:
-24/4/22 出1台(本廠-HA21032901-100002782-#2897-H08000808)
-25/3/24 出1台(3廠-HA21081701-100003244-000400001158)
-guang:
-25/10/29 研*1 OK(000400005984)
-11/3 出1台(本廠-HA22082901-100003402-000400002897)
-11/3 出1台(本廠-HA25102101-100003406-000400005984)</t>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-5/25 入1台(YZ)(NEW)
-8/9 入1台(YZ)(NEW)
-9/6 入1台(YZ)(NEW)
-9/27 入1台(YZ)(NEW)
-5/17 入2台(YZ)(NEW)
-6/10 入1台(YZ)(NEW)
-7/15 入1台(YZ)(NEW)
-7/16 入1台(YZ)(NEW)
-21/4/8 入1台(YZ)(NEW)
-4/19 入1台(YZ)(NEW)
-5/5 入1台(YZ)(NEW)
-5/6 入1台(YZ)(NEW)
-22/7/18 入1台(LD-#2926)
-8/12 入1台(LD-#3052)
-guang:
-23/2/10 入1台(LD-#3394)
-4/6 入1台(LD-#3463)
-24/11/15 入1台(LD-#5185)
-guang:
-12/18 入1台(LD-#5297)
-</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-7/6 M6*1OK(17M)(加工有問題)---OK    8/8M6*1OK(17M)
-8/9 M6*1OK(17M)
-6/21 M6*1 OK(17M)
-8/13 M6*1 OK(17M)
-8/14 M6*1 OK(17M)
-9/21 M6*1 OK(17M)
-10/12 M6*1 OK(17M)
-12/23 M6*1 OK(17M)
-12/25 M6*1 OK(17M)
-7/9 M6*1 OK(17M)
-7/27 M6*1 OK(17M)
-7/29 M6*1 OK(17M)
-21/4/13 M6*1 OK(17M)
-4/23 M6*1 OK(17M)
-8/30 M6*1 OK(17M-502)
-9/1 M6*1 OK(17M-658)
-22/7/23 M6*1 OK(17M-#2926)
-8/22 M6*1 OK(17M-#3052)
-23/2/20 M6*1 OK(17M-#3394)
-4/10 M6*1 OK(17M-#3463)
-24/11/21 M6*1 OK(17M-#5185)
-12/28 M6*1 OK(17M-#5297)
-</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-8/22 M5*1 OK(409)
-1/22 M5*1 OK(409)
-3/27 M5*1 OK(409)
-6/25 M5*1 OK(409)
-8/18 M5*1 OK(409)
-9/4 M5*1 OK(409)
-10/3 M5*1 OK(409)
-10/24 M5*1 OK(813)
-12/30 M5*1 OK(410)
-1/8 M5*1 OK(410)
-7/28 M5*1 OK(410)
-8/4 M5*1 OK(410)
-8/7 M5*1 OK(410)
-21/6/21 M5*1 OK(410-H08000810)
-6/24 M5*1 OK(410-H08000810)
-9/29 M5*1 OK(410-000400000658)
-10/4 M5*1 OK(410-000400000502)
-22/7/30 M5*1 OK(410-000400002926)
-9/15 M5*1 OK(410-000400003052)
-23/3/3 M5*1 OK(410-000400003394)
-4/17 M5*1 OK(410-000400003463)
-24/12/4 M5*1 OK(410-000400005185)
-25/1/8 M5*1 OK(410-000400005297)
-</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-9/8 研磨OK*1
-ralf:
-此庫存需搭配特殊版金 側邊
-guang:
-2/22 出1台(特殊 側邊板金)
-guang:
-5/17 出1台(三廠)
-5/24 出1台(三廠)
-7/9 出1台(三廠)
-8/30 研磨OK*1
-8/30 出1台(三廠)
-10/19 研磨OK*1
-11/16 研磨OK*1
-4/8 出1台(三廠-HA18090301)
-12/10 出1台(6路-HA18100302)
-2/19 出1台(6路-HA18102602)
-2/27 研磨OK*1
-4/9 出1台(6路-HA19123001-27838)
-8/21 研磨OK*1
-9/15 研磨OK*2
-9/30 出1台(6路-HA20080401-27839)
-guang:
-入*1(本廠退回)
-21/1/20 出1台(三廠-HA20080401-100000242)
-8/10 研磨OK*1(H080000810)
-8/26 出1台(三廠-HA20010801-100000941-000400000749)
-9/11 研磨OK*1(H080000810)
-10/20  研磨OK*1(000400000502)
-11/5  研磨OK*1(000400000658)
-22/1/4 出1台(本廠-HA20072801-100001266-000400000749)
-1/5 出1台(三廠-HA21062101-100000941-H080000810)
-1/7 出1台(三廠-HA20080701-100000902-000400000790)
-3/15 出1台(三廠-HA21100401-100001582-000400000502)
-5/9 出1台(三廠-HA21062401-100001583-H080000810)
-7/21 出1台(三廠-HA21092901-100001942-000400000790)
-9/1  研磨OK*1(000400002926)
-001289:
-11/11  研磨OK*1(000400003052)
-guang:
-23/1/5 出1台(三廠-HA22091501-100002087-000400003052)
-3/16 出1台(三廠-HA22073001-100002247-000400002926)
-4/13  研磨OK*1(000400003394)
-4/13 出1台(三廠-HA23030301-100002292-000400003394)
-6/5  研磨OK*1(000400003463)
-24/10/18 出1台(三廠-HA23041701-100002950-000400003463)
-12/27  研磨OK*1(000400005158)
-12/31 出1台(三廠-HA24120401-100003083-000400005185)
-001289:
-25/1/22 出1台(三廠-HA25010801-100002935-000400005297)
-</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:guang:
-3/17 入1支(CFC)
-3/20 入1支(CFC)
-3/21 入1台(YJF)
-3/23 入1台(YJF)
-3/28 入1台(YJF)
-3/30 入1台(YJF)
-4/10 入2台(YJF)
-4/27 入2支(CFC)
-6/1 入2支(YJF)
-7/20 入2支(YJF)
-7/27 入3支(YJF)
-8/11 入1台(CFC)
-9/20 入1台(CFC)(new)
-12/1 入1台(CFC)(new)
-12/21 入1台(CFC)(new)
-1/3 入1台(YJF)(new)
-1/10 入2支(YJF)(OLD)
-1/18 入1支(YJF)(OLD)
-1/18 入1台(CFC)(new)
-1/22 入1支(YJF)(OLD)
-1/23 入1台(CFC)(new)
-1/26 入1台(CFC)(new)
-1/31 入1台(CFC)(new)
-2/2 入1台(CFC)(new)
-3/14 入2台(CFC)(new)
-4/10 出2台(CFC)(轉隆升加工)
-4/11 出3台(CFC)(轉隆升加工)
-4/26 入2支(YJF)(NEW)
-4/30 入1台(YJF)(NEW)
-5/11 入2支(YJF)(NEW)
-5/17 入1台(YJF)(NEW)
-5/21 入1台(YJF)(NEW)
-5/24 出2台(YJF)(轉隆升加工)
-5/28 出3台(YJF)(轉隆升加工)
-5/31 入1台(YJF)(NEW)
-7/3 入2台(YJF)(NEW)
-11/19 入1台(CFC)(new)
-1/2 入3台(CFC)(new)
-3/25 入3台(CFC)(new)
-4/15 入2台(YJF)(NEW)
-4/29 入2台(YJF)(NEW)
-5/14 入1台(CFC)(NEW)
-5/28 入1台(CFC)(NEW)
-6/14 入1台(CFC)(NEW)
-6/20 入1台(YJF)(NEW)
-6/27 入1台(CFC)(NEW)
-6/28 入2台(YJF)(NEW)
-7/4 入1台(YJF)(NEW)
-8/28 入1台(CFC)(NEW)
-9/9 入1台(CFC)(NEW)
-1/9 入1台(CFC)(NEW)
-3/20 入2台(CFC)(NEW)
-3/24 入1台(CFC)(NEW)
-3/25 入1台(CFC)(NEW)
-4/8 入2台(CFC)(NEW)
-4/20 入1台(CFC)(NEW)
-8/27 入2台(CFC)(NEW)
-10/26 入2台(CFC)(NEW)
-11/26 入2台(CFC)(NEW)
-12/11 入2台(YJF)(NEW)
-21/2/2 入1台(YJF)(NEW)
-2/18 入1台(YJF)(NEW)
-2/23 入1台(YJF)(NEW)
-4/1 入1台(YJF)(NEW)
-5/11 入1台(YJF)(NEW)
-5/14 入1台(CFC)(NEW)
-5/19 入1台(YJF)(NEW)
-5/21 入1台(YJF)(NEW)
-6/2 入1台(YJF)(NEW)
-6/3 入1台(CFC)(NEW)
-6/15 入2台(YJF)(NEW)
-6/23 入1台(YJF)(NEW)
-7/2 入1台(CFC)(NEW)
-7/6 入3台(YJF)(NEW)
-22/3/3 入1台(CFC-#2393)
-3/3 入1台(CFC-#2394)
-5/23 入2台(CFC-#2787)
-6/9 入1台(CFC-#2855)
-hsin:
-6/13 入1台(YJF-#0962)
-8/25 入2台(YJF-#3076)
-23/4/7 入1台(CFC-#3472)
-5/2 入1台(CFC-#3515)
-5/17 入1台(CFC-#3556)
-6/13 入1台(CFC-#3617)
-7/25 入1台(CFC-#3731)
-24/1/10 入1台(CFC-#4225)
-5/15 入1台(YJF-#4570)
-7/9 入1台(CFC-#4784)
-7/11 入1台(CFC-#4815)
-8/1 入1台(CFC-#4869)
-8/2 入1台(YJF-#4864)
-9/3 入1台(CFC-#4953)
-guang:
-25/3/18 入2台(CFC-#5571)
-4/1 入1台(YJF-#5595)
-4/7 入1台(YJF-#5595)
-4/18 入1台(CFC-#5675)
-4/23 入1台(CFC-#5675)
-</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-8/1 M6*1 OK(17M)
-11/3 M6*1 OK(17M)
-11/4 M6*1 OK(17M)
-11/6 M6*1 OK(17M)
-1/29 M6*1ok(17M)(new)
-2/21 M6*1ok(17M)(new)
-2/22 M6*1ok(17M)(old)
-3/2 M6*2 OK(17M)(old)
-7/28 M6*1OK(17M)(new)
-7/30 M6*1OK(17M)(new)
-7/31 M6*1OK(17M)(new)
-9/25 M6*1OK(17M)(new)
-10/15 M6*1OK(17M)(new)-設變孔位
-10/16 M6*1OK(17M)(new)-設變孔位
-11/2 M6*1OK(17M)(new)-設變孔位
-11/12 M6*1OK(17M)(new)-設變孔位
-2/14 M6*1OK(17M)(new)-設變孔位
-2/15 M6*1OK(17M)(new)-設變孔位
-2/22 M6*1OK(17M)(new)-設變孔位
-2/23 M6*1OK(17M)(new)-設變孔位
-3/12 M6*1OK(17M)(new)-設變孔位
-3/13 M6*1OK(17M)(new)-設變孔位
-3/14 M6*1OK(17M)(new)-設變孔位
-4/17 M6*1OK(17M)(new)-設變孔位
-4/26 M6*2OK(17M)(new)
-6/12 M6-2*2 OK(408)(new)
-6/13 M6-2*2 OK(408)(new)
-6/26 M6-2*1 OK(408)(new)
-7/4 M6*1OK(17M)(new)
-7/5 M6*1OK(17M)(new)
-7/8 M6*1OK(17M)(new)
-7/9 M6*1OK(17M)(new)
-12/10 M6*1OK(17M)(new)
-12/12 M6*1OK(17M)(new)
-2/3 M6*1OK(17M)(new)
-4/27 M6*1OK(17M)(new)
-4/28 M6*1OK(17M)(new)
-5/4 M6*1OK(17M)(new)
-5/6 M6*1OK(17M)(new)
-5/7 M6*1OK(17M)(new)
-8/12 M6*1OK(17M)(new)
-8/14 M6*1OK(17M)(new)
-9/14 M6*1OK(17M)(new)
-9/17 M6*1OK(17M)(new)
-12/14 M6*1OK(17M)(new)
-12/16 M6*1OK(17M)(new)
-21/2/2 M6*1OK(17M)(new)
-2/4 M6*1OK(17M)(new)
-2/5 M6*1OK(17M)(new)
-2/17 M6*1OK(17M)(new)
-3/3 M6*1OK(17M)(H08000776)
-3/4 M6*1OK(17M)(H08000776)
-4/8 M6*1 OK(17M)(H08000776)
-5/24 M6*1 OK(17M)(H08000776)
-5/25 M6*1 OK(17M)(H08000776)
-5/26 M6*1 OK(17M)(000400000381)
-5/28 M6*1 OK(17M)(000400000381)
-6/19 M6*1 OK(17M)(000400000381)
-6/21 M6*1 OK(17M)(000400000730)
-6/22 M6*1 OK(17M)(000400000837)
-6/24 M6*1 OK(17M)(000400000381)
-6/26 M6*1 OK(17M)(000400000381)
-7/30 M6*1 OK(17M)(000400000381)
-8/3 M6*1 OK(17M)(000400001073)
-8/4 M6*1 OK(17M)(000400001103)
-8/27 M6*1 OK(17M)(000400001037)
-22/3/17 M6*1 OK(17M-#2394)
-3/19 M6*1 OK(17M-#2393)
-6/2 M6*1 OK(17M-#2787)
-6/7 M6*1 OK(17M-#2787)
-6/17 M6*1 OK(17M-#2855)
-6/28 M6*1 OK(17M-#962)
-9/1 M6*1 OK(17M-#3076)
-9/5 M6*1 OK(17M-#3076)
-23/4/12 M6*1 OK(17M-#3472)
-5/11 M6*1 OK(17M-#3515)
-6/28 M6*1 OK(17M-#3556)
-7/10 M6*1 OK(17M-#3617)
-8/1 M6*1 OK(17M-#3731)
-24/1/15 M6*1 OK(17M-#4225)
-5/27 M6*1 OK(17M-#4570)
-7/16 M6*1 OK(17M-#4815)
-7/17 M6*1 OK(17M-#4784)
-8/7 M6*1 OK(17M-#4869)
-8/9 M6*1 OK(17M-#4864)
-9/21 M6*1 OK(17M-#4953)
-guang:
-25/3/21 M6*1 OK(17M-#5571)
-3/25 M6*1 OK(17M-#5571)
-4/26 M6*1 OK(17M-#5675)
-4/29 M6*1 OK(17M-#5675)
-7/11 M6*1 OK(17M-#5595)
-7/16 M6*1 OK(17M-#5595)
-</t>
-      </text>
-    </comment>
-    <comment ref="F8" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-7/3 M5*1 OK (410)
-7/5 M5*1 OK (410)
-7/17 M5*1 OK (409)
-7/31 M5*1 OK (409)
-8/2 M5*1 OK (409)
-9/4 M5*1 OK (409)
-9/30 M5*1 OK(409) 
-10/3 M5*1 OK(409) 
-10/14 M5*1 OK(409) 
-10/30 M5*1 OK(409) 
-12/5 M5*1 OK(409)
-12/7 M5*1 OK(409) 
-12/21 M5*1 OK(409) 
-12/25 M5*1 OK(409) 
-1/24 M5*1 OK(409) 
-2/13 M5*1 OK(409) 
-3/1 M5*1 OK(409) 
-3/5 M5*1 OK(409) 
-3/17 M5*1 OK(409) 
-3/20 M5*1 OK(409)
-8/15 M5*1 OK(409)
-8/21 M5*1 OK(409)
-8/23 M5*1 OK(409)
-10/8 M5*1 OK(409)
-10/20 M5*1 OK(409)
-10/24 M5*1 OK(409)
-10/27 M5*1 OK(409)
-10/30 M5*1 OK(409)
-2/20 M5*1 OK(410)
-2/23 M5*1 OK(410)
-3/7 M5*1 OK(410)
-3/11 M5*1 OK(410)
-3/21 M5*1 OK(410)
-3/29 M5*1 OK(410)
-4/2 M5*1 OK(410)
-5/7 M5*1 OK(410)
-5/9 M5*1 OK(410)
-5/14 M5*1 OK(410)
-6/14 M5*1 OK(410)
-6/20 M5*1 OK(410)
-6/25 M5*1 OK(410)
-6/27 M5*1 OK(410)
-7/3 M5*1 OK(410)
-8/6 M5*1 OK(410)
-8/13 M5*1 OK(410)
-8/21 M5*1 OK(410)
-8/29 M5*1 OK(410)
-9/6 M5*1 OK(410)
-12/17 M5*1 OK(410)
-12/24 M5*1 OK(410)
-2/21 M5*1 OK(410)
-6/3 M5*1 OK(410)
-6/9 M5*1 OK(410)
-7/2 M5*1 OK(410)
-7/8 M5*1 OK(410)
-9/17 M5*1 OK(410)
-9/23 M5*1 OK(410)
-9/30 M5*1 OK(410)
-10/8 M5*1 OK(410)
-10/15 M5*1 OK(410)
-21/1/6 M5*1 OK(410)
-1/13 M5*1 OK(410)
-1/19 M5*1 OK(410)
-2/18 M5*1 OK(410)
-2/22 M5*1 OK(410)
-2/24 M5*1 OK(410)(HA21022401-000400000175)
-3/3 M5*1 OK(410)
-3/8 M5*1 OK(410)(HA21030801-H08000776)
-3/12 M5*1 OK(410-H08000776)
-5/14 M5*1 OK(410-H08000776)
-6/4 M5*1 OK(410-H08000776)
-6/8 M5*1 OK(410-H08000776)
-6/11 M5*1 OK(410-000400000381)
-6/16 M5*1 OK(410-000400000381)
-6/28 M5*1 OK(410-000400000381)
-7/1 M5*1 OK(410-000400000381)
-7/6 M5*1 OK(410-000400000381)
-7/20 M5*1 OK(410-000400000730)
-8/2 M5*1 OK(410-000400000837)
-8/10 M5*1 OK(410-000400001073)
-8/27 M5*1 OK(410-000400000381)
-8/31 M5*1 OK(410-000400001103)
-9/3 M5*1 OK(410-000400001037)
-22/3/26 M5*1 OK(410-000400002394)
-3/30 M5*1 OK(410-000400002393)
-6/17 M5*1 OK(410-000400002787)
-6/22 M5*1 OK(410-000400002787)
-6/25 M5*1 OK(410-000400002855)
-7/22 M5*1 OK(410-000400000962)
-9/27 M5*1 OK(410-000400003076)
-10/3 M5*1 OK(410-000400003076)
-23/4/21 M5*1 OK(410-000400003472)
-6/30 M5*1 OK(410-000400003515)
-7/6 M5*1 OK(410-000400003556)
-8/4 M5*1 OK(410-000400003617)
-8/14 M5*1 OK(410-000400003731)
-24/2/20 M5*1 OK(410-000400004225)
-6/25 M5*1 OK(410-000400004570)
-7/23 M5*1 OK(410-000400004815)
-7/30 M5*1 OK(410-000400004784)
-8/22 M5*1 OK(410-000400004864)
-8/28 M5*1 OK(410-000400004869)
-9/27 M5*1 OK(410-000400004953)
-guang:
-25/4/24 M5*1 OK(410-000400005571)
-4/29 M5*1 OK(410-000400005571)
-5/16 M5*1 OK(410-000400005675)
-5/22 M5*1 OK(410-000400005675)
-7/31 M5*1 OK(410-000400005595)
-9/9 M5*1 OK(410-000400005595)
-</t>
-      </text>
-    </comment>
-    <comment ref="G8" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-1/21 出1台(三廠-HA19080602)
-2/6 出1台(三廠-HA19082901)
-3/2 出1台(三廠-HA19082101)
-3/11 出1台(三廠-HA19070301)
-3/12 研磨OK*1
-3/20 研磨OK*1
-3/24 研磨OK*1
-3/25 研磨OK*1
-3/30 出1台(三廠-HA190121701)
-6/18 研磨OK*1
-6/23 出1台 (本廠-HA20060301-機號:27836)
-7/21 研磨OK*1
-7/28 研磨OK*1
-7/30 出1台 (本廠-HA20060901-機號:28231)
-8/7 研磨OK*1
-8/21 出1台 (三廠-HA20070201-機號:27877)
-8/26 出1台 (本廠-HA20070801-機號:27837)
-10/23 出1台 (本廠-HA19090501-機號:27878)
-10/26 出1台(三廠-HA19070401-機號28320)
-10/26 出1台(三廠-HA20022101-機號28321)
-10/29 研磨OK*1
-11/2 出1台(三廠-HA20091701-機號28325)
-11/12 研磨OK*1
-11/13 出1台(三廠-HA20092301-機號27912)
-11/18 研磨OK*1
-12/22 研磨OK*1
-21/1/7 出1台(三廠-HA20093001-機號28316)
-21/1/7 出1台(三廠-HA20101601-機號28317)
-12/30 研磨OK*1
-21/1/15 出1台(三廠-HA20100801-配100000205)
-1/25 研磨OK*1
-1/28 出1台(三廠-HA21010901-配100000206)
-21/2/4 研磨OK*1
-2/4 出1台(三廠-HA21011301-配100000296)
-2/5 研磨OK*1
-2/5 出1台(三廠-HA21011901-配100000243)
-2/24 研磨OK*1
-2/25 出1台(三廠-HA21021801-配100000244)
-3/8 研磨OK*1
-3/9 出1台(三廠-HA21022201-配100000249)
-3/25 研磨OK*1
-4/1 出1台(三廠-HA21022401-配100000544-000400000175)
-3/26 研磨OK*1
-4/14 研磨OK*1
-4/29 研磨OK*1
-5/12 出1台(三廠-HA21030301-配100000629)
-5/14 出1台(三廠-HA21030801-100000630-H08000776)
-6/8 研磨OK*1(H08000776)
-7/2 出1台(三廠-HA21031201-100000919-H08000776)
-7/1 研磨OK*2(000400000381*2)
-7/10 研磨OK*2(H08000776*2)
-8/25 出1台(三廠-HA21060801-100000743-H08000776)
-9/29 研磨OK*1(000400000730*1)
-9/29 研磨OK*1(000400000381*1)
-10/12 出1台(三廠-HA21070601-100000967-000400000381)
-10/26 研磨OK*1(000400001103*1)
-11/4 出1台(三廠-HA21051401-100001062-H08000776)
-11/9 出1台(三廠-HA21083101-100000181-000400001103)
-12/2 出1台(三廠-HA21061101-100001313-000400000381)
-12/9 出1台(三廠-HA21061601-100001332-000400000381)
-22/2/14 研磨OK*2(000400001037*1-#381)
-2/16 研磨OK*1(000400000837)
-3/8 出1台(三廠-HA21082701-100001334-000400000381)
-4/7 出1台(三廠-HA21080201-100001686-000400000837)
-4/25 出1台(三廠-HA21060401-100001741-H08000776)
-5/3 出1台(三廠-HA21070201-100001743-000400000730)
-5/14 出1台(三廠-HA21030801-100000630-H08000776)
-6/8 研磨OK*1(H08000776)
-7/2 出1台(三廠-HA21031201-100000919-H08000776)
-7/1 研磨OK*2(000400000381*2)
-7/10 研磨OK*2(H08000776*2)
-8/25 出1台(三廠-HA21060801-100000743-H08000776)
-9/29 研磨OK*1(000400000730*1)
-9/29 研磨OK*1(000400000381*1)
-10/12 出1台(三廠-HA21070601-100000967-000400000381)
-10/26 研磨OK*1(000400001103*1)
-11/4 出1台(三廠-HA21051401-100001062-H08000776)
-11/9 出1台(三廠-HA21083101-100000181-000400001103)
-12/2 出1台(三廠-HA21061101-100001313-000400000381)
-12/9 出1台(三廠-HA21061601-100001332-000400000381)
-22/2/14 研磨OK*2(000400001037*1-#381)
-2/16 研磨OK*1(000400000837)
-3/8 出1台(三廠-HA21082701-100001334-000400000381)
-4/7 出1台(三廠-HA21080201-100001686-000400000837)
-4/25 出1台(三廠-HA21060401-100001741-H08000776)
-5/3 出1台(三廠-HA21070201-100001743-000400000730)
-5/13 出1台(三廠-HA21090301-100001453-000400001037)
-5/9 研磨OK*1(000400002394)
-5/17 出1台(三廠-HA22032601-100001454-000400002394)
-5/24 研磨OK*2(000400000381*2)
-6/9 研磨OK*1(000400002393)
-6/15 研磨OK*1(000400001073)
-7/20 出1台(三廠-HA21062801-100001820-000400000381)
-8/5 研磨OK*2(000400002787*2)
-001289:
-10/20 出1台(三廠-HA22033001-100001958-000400002393)
-guang:
-10/26 出1台(三廠-HA21070501-100002000-000400000381)
-001289:
-10/26 研磨OK*1(000400003076*1)
-11/14 出1台(三廠-HA22092701-100002093-000400003076)
-11/28 研磨OK*1(000400000962*1)
-12/8 研磨OK*1(000400003076*1)
-23/1/30 出1台(三廠-HA22100301-100002156-000400003076)
-12/8 研磨OK*1(000400000962*1)
-23/3/24 出1台 (本廠-HA21081001-100002293-000400001073)
-4/10 出1台(三廠-HA22072101-100002291-000400000962)
-5/2 出1台(三廠-HA22061701-100002373-000400002787 )
-5/18 出1台(三廠-HA22062201-100002275-000400002787 )
-5/22 研磨OK*1(#2855*1，#3472*1)
-7/31 研磨OK*1(#3556*1)
-8/1 研磨OK*1(#3515*1)
-8/24 出1台(三廠-HA23063001-100002544-000400003515)
-9/5 研磨OK*1(#3617*1)
-9/11 出1台(三廠-HA21082501-100002546-000400002855)
-9/14 研磨OK*1(#3731*1)
-10/2 出1台(三廠-HA23042101-100002565-000400003472)
-10/27 出1台(三廠-HA23070601-100002562-000400003556)
-12/6 出1台(三廠-HA23081401-100002632-000400003731)
-24/4/15 研磨OK*1(#4225)
-4/25 出1台(三廠-HA23080401-100002813-000400003617)
-5/22 出1台(三廠-HA24022001-100002779-000400004225)
-7/8 研磨OK*1(#4570)
-7/12 出1台(本廠-HA24062501-100002872-000400004570)
-8/2 研磨OK*1(#4815)
-8/6 出1台(三廠-HA24072301-100002724-000400004815)
-8/12 研磨OK*1(#4784)
-9/3 研磨OK*1(#4864)
-11/14 研磨OK*1(#4869)
-11/19 出1台(三廠-HA24073001-100003043-000400004784)
-guang:
-12/3 研磨OK*1(#4953)
-25/2/7 出1台(廠內展用-三廠-HA24082201-100003170-000400004864)
-2/8 出1台(廠內展用-三廠-HA24082801-100003168-000400004869)
-2/20 出1台(三廠-HA24092701-100003125-000400004953)
-6/2 研磨OK*1(#5571)
-6/5 出1台(三廠-HA25042301-100003321-000400005571)
-6/10 研磨OK*1(#5571)
-6/18 研磨OK*1(#5675)
-7/10 研磨OK*1(#5675)
-9/18 研磨OK*1(#5595)
-9/19 出1台(三廠-HA25052201-100003401-000400005675)
-       研磨OK*1(#5595)
-</t>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-4/7 入1台(YZ)
-4/17 入1台(YZ)
-4/25 入1台(YZ)
-4/28 入1台(YZ)
-5/24 入1台(YZ)
-6/26 入1台(YZ)(NEW)
-7/10 入1台(YZ)(NEW)
-8/9 入1台(YZ)(NEW)
-8/28 入1台(YZ)(NEW)
-11/13 入1台(YZ)(NEW)
-1/4 入2台(YZ)(NEW)
-1/19 入1台(YZ)(NEW)
-1/22 入1台(YZ)(NEW)
-2/2 入2台(YZ)(NEW)
-2/21 入3台(YZ)(NEW)
-5/9 入1台(YZ)(NEW)
-5/10 入1台(YZ)(NEW)
-7/10 入1台(YZ)(NEW)
-7/24 入1台(YZ)(NEW)
-7/26 入1台(YZ)(NEW)
-8/7 入1台(YZ)(NEW)
-8/21 入1台(YZ)(NEW)
-9/4 入1台(YZ)(NEW)
-11/29 入1台(YZ)(NEW)
-12/4 入1台(YZ)(NEW)
-1/2 入1台(YZ)(NEW)
-1/3 入1台(YZ)(NEW)
-1/7 入1台(YZ)(NEW)
-1/9 入1台(YZ)(NEW)
-2/25 入2台(YZ)(NEW)
-3/27 入1台(YZ)(NEW)
-4/8 入1台(YZ)(NEW)
-7/2 入2台(YZ)(NEW)
-9/25 入1台(YZ)(NEW)
-9/30 入1台(YZ)(NEW)
-12/18 入1台(YZ)(NEW)
-6/23 入2台(YZ)(NEW)
-8/28 入1台(YZ)(NEW)
-9/10 入1台(YZ)(NEW)
-21/4/8 入1台(YZ)(NEW)
-4/20 入1台(YZ)(NEW)
-5/3 入1台(YZ)(NEW)
-5/4 入1台(YZ)(NEW)
-10/1 入1台(YZ)(NEW)
-10/4 入1台(YZ)(NEW)
-10/14 入1台(YZ)(NEW)
-10/15 入1台(YZ)(NEW)
-10/26 入1台(YZ)(NEW)
-22/3/28 入1台(YZ-#2508)
-4/1 入1台(YZ-#2548)
-6/2 入1台(LD-#2766)
-6/8 入1台(LD-#2766)
-7/1 入1台(LD-#2899)
-7/11 入1台(LD-#2925)
-7/12 入1台(LD-#2925)
-guang:
-24/8/2 入1台(LD-#4882)
-8/8 入1台(LD-#4882)
-10/29 入1台(LD-#5099)
-12/5 入1台(LD-#5173)
-12/9 入1台(LD-#5236)
-001289:
-25/1/21 入1台(LD-#5392)
-26/1/9 入1台(#5099)(補)</t>
-      </text>
-    </comment>
-    <comment ref="E9" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/11 M6*1 ok(17M)
-4/22 M6*1 ok(17M)
-5/17 M6*1 ok(17M)
-5/18 M6*1 ok(17M)
-6/16 M6*1 ok(17M)
-7/4M6*1ok(17M)(new)
-7/13M6*1ok(17M)(new
-8/10 M6*1OK(17米) 
-9/8 M6*1OK(17米)
-11/22 M6*1OK(17米)
-1/10 M6*1ok(17M)(new)
-1/11 M6*1ok(17M)(new)
-1/29 M6*1ok(17M)(new)
-3/5 M6*1ok(17M)(new)
-3/27 M6*1ok(17M)(new)
-5/8 M6*1ok(17M)(new)
-5/9 M6*1ok(17M)(new)
-5/17 包砂太多(退)(YZ)
-6/1 M6*1ok(17M)(new)
-6/4 M6*1ok(17M)(new)
-6/23 M6*1 OK(17M)
-7/23 M6*1 OK(17M)
-7/24 M6*1 OK(17M)
-9/27 M6*1 OK(17M)
-10/1 M6*1 OK(17M)
-10/17 M6*1 OK(17M)
-10/18 M6*1 OK(17M)
-10/22 M6*1 OK(17M)
-12/26 M6*1 OK(17M)
-12/28 M6*1 OK(17M)
-1/29 M6*1 OK(17M)
-1/31 M6*1 OK(17M)
-2/12 M6*1 OK(17M)
-2/13 M6*1 OK(17M)
-5/2 M6*1 OK(17M)
-6/25 M6*2 OK(408-M6-2)
-7/3 M6*1 OK(17M)
-7/29 M6*1 OK(409-M6-1)
-8/6 M6*1 OK(408-M6-2)
-8/12 M6*1 OK(409-M6-1)
-10/16 背面包砂(報廢)
-11/1 出1台(報廢-永棧)
-11/12 入1台(報廢-永棧)
-11/13 M6*1 OK(409-M6-1)
-11/15 M6*1 OK(409-M6-1)
-11/15 M6*1 OK(523-M6-2)
-11/18 M6*1 OK(523-M6-2)
-11/19 M6*1 OK(523-M6-2)
-12/31 M6*1 OK(17M)
-7/2 M6*1 OK(17M)
-7/6 M6*1 OK(17M)
-9/22 M6*1 OK(17M)
-9/29 M6*1 OK(17M)
-21/4/15 M6*1 OK(17M)
-4/28 M6*1 OK(17M)
-5/13 M6*1 OK(17M-報廢)
-5/17 M6*1 OK(17M)
-6/2 出1台(YZ載回)
-10/6 M6*1 OK(17M-732)
-10/8 M6*1 OK(17M-732)
-11/8 M6*1 OK(17M-1735)
-11/10 M6*1 OK(17M-1794)
-11/13 M6*1 OK(17M-1798)
-22/4/13 M6*1 OK(17M-#2548)
-4/23 M6*1 OK(17M-#2508)
-6/13 M6*1 OK(17M-#2766)
-6/16 M6*1 OK(17M-#2766)
-7/15 M6*1 OK(17M-#2899)
-7/19 M6*1 OK(17M-#2925)
-7/21 M6*1 OK(17M-#2925)
-24/8/5 M6*1 OK(17M-#4882)
-8/12 M6*1 OK(17M-#4882)
-11/6 M6*1 OK(17M-#5099)
-25/1/6 M6*1 OK(17M-#5173)
-2/10 M6*1 OK(17M-#5236)
-5/17 M6*1 OK(17M-#5392)
-</t>
-      </text>
-    </comment>
-    <comment ref="F9" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-4/17 M5*1OK(410)
-5/4 M5*1 OK(410)
-5/24 M5*1 OK(410)
-5/26 M5*1 OK(410)
-6/23 M5*1 OK(410)
-7/11 M5*1 OK(409)
-7/20 M5*1 OK(409)
-8/18 M5*1 OK(409)
-9/26 M5*1 OK(409)
-11/30 M5*1 OK(409)
-1/12 M5*1 OK(409)
-1/16 M5*1 OK(409)
-2/9 M5*1 OK(409)
-3/9 M5*1 OK(409)
-4/3 M5*1 OK(409)
-5/14 M5*1 OK(409)
-6/6 M5*1 OK(409)
-6/8 M5*1 OK(409)
-7/5 M5*1 OK(409)
-8/10 M5*1 OK(813)
-8/13 M5*1 OK(813)
-10/11 M5*1 OK(409)
-10/15 M5*1 OK(409)
-10/26 M5*1 OK(409)
-10/30 M5*1 OK(813)
-11/1 M5*1 OK(409)
-1/7 M5*1 OK(409)
-1/9 M5*1 OK(409)
-2/13 M5*1 OK(410)
-2/15 M5*1 OK(410)
-3/14 M5*1 OK(410)
-3/19 M5*1 OK(410)
-5/21 M5*1 OK(410)
-7/1 M5*1 OK(813)
-7/5 M5*1 OK(813)
-7/10 M5*1 OK(813)
-9/30 M5*1 OK(410)
-11/27 M5*1 OK(410)-#1856
-12/4 M5*1 OK(410)
-12/11 M5*1 OK(410)
-1/16 M5*1 OK(410)
-7/14 M5*1 OK(410)
-7/21 M5*1 OK(410)
-11/26 M5*1 OK(410)
-12/10 M5*1 OK(410)
-21/5/10 M5*1 OK(410-H08000786)
-5/19 M5*1 OK(410-H08000785)
-5/24 M5*1 OK(410-000400000649)
-10/13 M5*1 OK(410-000400000732)
-10/19 M5*1 OK(410-000400000732)
-11/18 M5*1 OK(410-000400001794)
-11/24 M5*1 OK(410-000400001798)
-12/7 M5*1 OK(410-000400001735)
-22/5/3 M5*1 OK(410-000400002548)
-5/6 M5*1 OK(410-000400002508)
-7/6 M5*1 OK(410-000400002766)
-7/12 M5*1 OK(410-000400002766)
-7/26 M5*1 OK(410-000400002925)
-8/4 M5*1 OK(410-000400002899)
-8/8 M5*1 OK(410-000400002925)
-guang:
-24/8/12 M5*1 OK(410-#4882)
-8/16 M5*1 OK(410-#4882)
-11/14 M5*1 OK(410-#5099)
-25/1/15 M5*1 OK(410-#5173)
-2/27 M5*1 OK(410-#5236)
-6/27 M5*1 OK(410-#5392)
-</t>
-      </text>
-    </comment>
-    <comment ref="G9" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-2/23 出1台
-4/6  出1台(三廠)
-ralf:
-4/27 研磨OK*1(7018)
-5/9 出1台
-6/7 研磨OK*1(7018)
-6/8 研磨OK*1(7018)
-6/16  出1台
-6/30  出1台
-7/4  出1台
-7/25  出1台
-7/27  出1台
-7/31 研磨OK*1
-8/8  出1台
-9/7研磨OK*1
-9/25  出1台
-10/26  出1台
-12/6  研磨OK*1
-12/6  出1台
-1/19  出1台
-3/23 出1台
-3/27 研磨OK*1
-4/24 出1台(三廠)
-7/25 出1台(三廠)
-8/8 出1台(三廠)
-9/3 出1台(三廠)
-9/13 出1台(三廠)-5BC
-9/14 出1台(三廠)
-10/22 研磨OK*1
-10/22 出1台(三廠)
-10/23 研磨OK*1
-10/23 出1台(三廠)
-11/8 研磨OK*1
-11/21 研磨OK*1
-11/29 研磨OK*1-5BC
-12/12 出1台(三廠)
-12/14 出1台 (6路)-5BC
-12/20 出1台(三廠)
-2/1 研磨OK*2-5BC
-3/14 研磨OK*1
-3/25 出1台(三廠-HA19010901-5BC)
-4/12 出1台(三廠-HA19021301)
-5/7 研磨OK*1
-5/7 出1台(三廠-HA19021502)
-5/17 研磨OK*1
-6/5 出1台(三廠-HA19010702-5BC)
-6/5 研磨OK*1
-6/14 研磨OK*1-5BC
-6/17 出1台(三廠-HA19052102-5BC)
-6/25 出1台(三廠-HA19031402)
-7/19 出1台(三廠-HA19031901)
-7/22 研磨OK*1-5BC
-7/27 研磨OK*1-5BC
-8/28 研磨OK*1
-9/11 出1台(三廠-HA19070501-5BC)
-10/31 研磨OK*1
-1/2 研磨OK*1
-1/15 出1台(三廠-HA19071002)
-1/30 出1台(三廠-HA19093001)
-2/7 研磨OK*1
-2/26 研磨OK*1
-4/14 研磨OK*1
-6/3 出1台(本廠-HA19120401-機號:28132)
-8/4 出1台(本廠-HA20011601-機號:28228)
-8/18 出1台(三廠-HA19121101-機號:27906)
-9/4 研磨OK*1
-9/10 研磨OK*1
-12/4 出1台(三廠-HA20072101-機號:27811)
-12/17 出1台(三廠-HA20071401-機號:27767)(預開)
-21/1/8 出1台(三廠-HA20071401-機號:100000183)
-2/2 研磨OK*1
-2/3 研磨OK*1
-2/17 出1台(三廠-HA20121101-機號:100000354)
-3/11 出1台(三廠-HA20112601-機號:100000279-H08000786)
-內含2台5BC專用
-5/18 研磨OK*1
-5/19 出1台(三廠-HA21051001-100000764-H08000786)
-6/2 研磨OK*2-H08000785*1,000400000649*1
-6/21 出1台(三廠-HA21051801-100000721-H08000785)
-12/1 研磨OK*1(000400000732)
-12/14 出1台(三廠-HA21101301-100001368-000400000732)
-12/23 研磨OK*1(000400000732)
-22/1/5 出1台(三廠-HA21052401-100001364-000400000649)客制化
-1/7 出1台(三廠-HA21101901-100001369-000400000732)
-1/13 研磨OK*1(000400001794)
-1/27 出1台(三廠-HA21111801-100001173-000400001794)
-2/17 研磨OK*1(000400001735)
-2/21 出1台(三廠-HA21120701-100001541-000400001735)
-3/2 研磨OK*1(000400001798)
-3/31 出1台(三廠-HA19070101-100001159-000400001744-5BC)
-5/25 出1台(三廠-HA21112401-100001790-000400001798)
-6/7 研磨OK*1(000400002548)
-6/13 出1台(三廠-HA22050301-100001760-000400002548)
-6/9 研磨OK*1(000400002508)
-7/13 出1台(三廠-HA22050601-100001902-000400002508)
-7/29 研磨OK*2(000400002766*2)
-9/1 研磨OK*1(000400002925)
-9/19 研磨OK*1(000400002899)
-guang:
-23/1/3 出1台(三廠-HA22070601-100002195-000400002766)
-2/17 出1台(三廠-HA19112701-100001952-000400001856-5BC)
-guang:
-3/27 出1台(三廠-HA22072601-100002319-000400002925)
-5/19 研磨OK*1(000400002925)
-5/30 出1台(三廠-HA22080801-100002408-000400002925)
-10/11 出1台(三廠-HA22071201-100002308-000400002766-5BC)
-10/24 出1台(三廠-HA22080301-100002577-000400002899)
-8/20 研磨OK*1(000400004882)
-8/21 出1台(三廠-HA24081201-100002747-000400004882)
-9/2 研磨OK*1(000400004882)
-9/2 出1台(三廠-HA24081601-100002919-000400004882)
-12/26 研磨NG*1(000400005099)
-25/2/21 研磨OK*1(000400005173)
-3/28 研磨OK*1(000400005236)
-8/14 出1台(三廠-HA25011501-100003378-000400005173)
-8/8 研磨OK*1(000400005392)
-10/22 出1台(3廠-HA25062701-100003418-000400005392)
-</t>
-      </text>
-    </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
-      <text>
-        <t>hsinwei:
-12/26 研磨NG*1(000400005099)(斜面上端裂痕品管判定報廢)
-26/1/8 出1台(#5099)</t>
-      </text>
-    </comment>
-    <comment ref="C10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/27 入2台(JS)
-3/30 入2台(JS)
-4/5 入2台(YZ)
-4/11 入1台(JS)
-4/17入2(JS)
-4/19 入1(JS)
-11/9 入1台(YZ)
-11/29 入1台(YZ)(新)
-12/7 入1台(YZ)(新)
-01/02 入1台(YZ)(new)
-01/02 入1台(js)(new)
-01/04 入1台(js)(new)
-1/8 入1台(JS)(NEW)
-1/8 入1台(YZ)(NEW)
-1/11 入1台(JS)(NEW)
-1/15 入1台(YZ)(NEW)
-1/29 入1台(YZ)(NEW)
-2/2 入1台(JS)(NEW)
-2/5 入1台(JS)(NEW)
-2/13 入2台(JS)(NEW)
-2/21 入1台(YZ)(NEW)
-3/12 入1台(JS)(NEW)
-3/19 入2台(JS)(NEW)
-3/23 入1台(JS)(NEW)
-ralf:
-5/16廣場盤點有3隻
-guang:
-5/23 入1台(JS)(NEW)
-6/1 入1台(JS)(NEW)
-6/13 入1台(JS)(NEW)
-6/26 入1台(JS)(NEW)
-10/23 入1台(JS)(NEW)(換)
-11/22 入1台(YZ)(NEW)
-11/27 入1台(YZ)(NEW)
-12/12 入1台(YZ)(NEW)
-12/13 入1台(YZ)(NEW)
-12/19 入2台(YZ)(NEW)
-2/18 入1台(YZ)(NEW)
-2/21 入1台(YZ)(NEW)
-2/26 入1台(YZ)(NEW)
-3/4 入1台(YZ)(NEW)
-3/8 入1台(YZ)(NEW)
-3/15 入1台(YZ)(NEW)
-6/6 入1台(JS)(NEW)
-6/11 入1台(JS)(NEW)
-7/2 入1台(YZ)(NEW)
-7/3 入1台(YZ)(NEW)
-7/15 入1台(JS)(NEW)
-7/22 入1台(JS)(NEW)
-1/10 入1台(YZ)(NEW)
-3/25 入1台(YZ)(NEW)
-5/5 入1台(YZ)(NEW)
-5/11 入1台(YZ)(NEW)
-6/10 入1台(YZ)(NEW)
-9/18 入1台(YZ)(NEW)
-10/5 入1台(YZ)(NEW)
-10/21 入1台(YZ)(NEW)
-11/20 入1台(YZ)(NEW)
-11/27 入1台(YZ)(NEW)
-12/2 入1台(YZ)(NEW)
-21/6/30 入1台(YZ)(NEW)
-7/8 入1台(YZ)(NEW)
-7/14 入1台(YZ)(NEW)
-7/26 入1台(YZ)(NEW)
-8/4 入1台(YZ)(NEW)
-12/13 入1台(YZ-2041)
-22/1/4 入1台(YZ-1384)
-1/7 入1台(YZ-2120)
-2/7 入1台(YZ-2250)
-2/15 入1台(JS-2082)
-2/18 入1台(YZ-#2305)
-3/3 入1台(JS-#2082)
-3/8 入1台(JS-#2082)
-3/11 入1台(JS-#2082)
-24/5/6 入1台(LD-#4595)
-5/23 入1台(LD-#4595)
-5/30 入1台(LD-#4671)
-6/3 入1台(LD-#4671)
-10/16 入1台(LD-#5054)
-guang:
-2025/1/2 入2台(LD-#5346)
-2/11 入1台(LD-#4671)(補)
-2/17 入1台(LD-#5404)
-2/18 入1台(LD-#5471)
-2/20 入2台(LD-#5478)
-guang:
-</t>
-      </text>
-    </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/13 M6*1 OK(17M)
-3/14 M6*1 OK(17M)
-4/13 M6*1 OK(17M)
-5/8  M6*2 OK(17M)
-5/20  M6*1 OK(17M)
-6/14  M6*1 OK(17M)
-6/15  M6*1 OK(17M)
-7/14  M6*1 OK(17M)
-7/20  M6*1 OK(17M)
-11/14  M6*1 OK(17M)
-12/11  M6*1 OK(17M)
-12/13  M6*1 OK(17M)
-1/12  M6*1 OK(17M)
-1/24  M6*1 OK(17M)
-1/25  M6*1 OK(17M)
-1/26  M6*1 OK(17M)
-2/23 M6*1 OK(17M)
-3/5 M6*1 OK(17M)
-3/14 M6*1 OK(17M)
-3/26 M6*1 OK(17M)
-3/27 M6*1 OK(17M)
-4/9 M6*1 OK(17M)
-4/10 M6*1 OK(17M)
-4/11 M6*1 OK(17M)
-4/26 M6*1 OK(17M)
-4/27 M6*1 OK(17M)
-5/4 M6*1 OK(17M)
-5/5 M6*1 OK(17M)
-6/29 M6*1 OK(17M)
-7/11 M6*1 OK(17M)
-7/12 M6*1 OK(17M)
-7/13 M6*1 NG(17M)(翻鑄不良)
-7/14 M6*1 OK(17M)
-guang:
-7/16 出1台(JS)(翻鑄不良)
-8/31 M6*1 OK(17M)
-9/3 M6*1 OK(17M)
-11/01 M6*1 OK(17M)
-12/13 M6*1 OK(17M)
-12/14 M6*1 OK(17M)
-12/17 M6*1 OK(17M)
-1/8 M6*1 OK(17M)
-1/9 M6*1 OK(17M)
-1/10 M6*1 OK(17M)
-1/14 M6*1 OK(17M)
-3/15 M6*1 OK(17M)
-3/16 M6*1 OK(17M)
-3/26 M6*1 OK(17M)
-3/27 M6*1 OK(17M)
-3/28 M6*1 OK(17M)
-4/30 M6*1 OK(17M)
-7/19 M6*1 OK(523 M6-1)
-7/22 M6*1 OK(523 M6-1)
-7/23 M6*1 OK(523 M6-1)
-7/24 M6*1 OK(523 M6-1)
-7/23 M6*1 OK(408 M6-2)
-7/25 M6*1 OK(523 M6-1)
-7/26 M6*1 OK(408 M6-2)
-10/15 M6*1 OK(17M)
-1/21 M6*1 OK(17M)
-4/20 M6*1 OK(17M)
-5/12 M6*1 OK(17M)
-5/13 M6*1 OK(17M)
-8/3 M6*1 OK(17M)
-10/6 M6*1 OK(17M)
-10/8 M6*1 OK(17M)
-11/2 M6*1 OK(17M)
-12/3 M6*1 OK(17M)
-12/8 M6*1 OK(17M)
-12/10 M6*1 OK(17M)
-21/7/2 M6*1 OK(17M)
-7/16 M6*1 OK(17M-1184)
-7/19 M6*1 OK(17M-1239)
-7/29 M6*1 OK(17M-1265)
-8/6 M6*1 OK(17M-1330)
-12/27 M6*1 OK(17M-2041)
-22/1/11 M6*1 OK(17M-1384)
-1/13 M6*1 OK(17M-2120)
-2/22 M6*1 OK(17M-2250)
-2/24 M6*1 OK(17M-2305)
-2/26 M6*1 OK(17M-2082)
-3/7 M6*1 OK(17M-2082)
-3/22 M6*1 OK(17M-2082)
-5/7 M6*1 OK(17M-2082)
-24/5/15 M6*1 OK(17M-#4595)
-5/30 M6*1 OK(17M-#4595)
-6/18 M6*1 OK(17M-#4671)
-10/22 M6*1 OK(17M-#5054)
-25/1/9 M6*1 OK(17M-#5346)
-1/13 M6*1 OK(17M-#5346)
-2/24 M6*1 OK(17M-#4671)
-2/26 M6*1 OK(17M-#5478)
-7/4 M6*1 OK(17M-#5404)
-7/9 M6*1 OK(17M-#5471)
-</t>
-      </text>
-    </comment>
-    <comment ref="F10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/6  M5*1 OK(410)
-4/21  M5*1 OK(410)
-5/10  M5*1 OK(410)
-5/12  M5*1 OK(410)
-6/8  M5*1 OK(410)
-6/19  M5*1 OK(410)
-6/21  M5*1 OK(410)
-8/4  M5*1 OK(409)
-8/8  M5*1 OK(409)
-8/11  M5*1 OK(409)
-11/20 M5*1 OK(409)
-12/15 M5*1 OK(409)
-12/19 M5*1 OK(409)
-1/18 M5*1 OK(409)
-1/31 M5*1 OK(410)
-2/22 M5*1 OK(409)
-2/24 M5*1 OK(409)
-3/7 M5*1 OK(409)
-3/15 M5*1 OK(409)
-3/22 M5*1 OK(409)
-3/29 M5*1 OK(409)
-3/31 M5*1 OK(409)
-4/18 M5*1 OK(409)
-4/20 M5*1 OK(409)
-5/4 M5*1 OK(409)
-5/8 M5*1 OK(409)
-5/10 M5*1 OK(409)
-5/16 M5*1 OK(409)
-5/18 M5*1 OK(409)
-7/11 M5*1 OK(409)
-7/19 M5*1 OK(409)
-7/23 M5*1 OK(409)
-7/25 M5*1 OK(409)
-9/6 M5*1 OK(409)
-9/10 M5*1 OK(409)
-12/12 M5*1 OK(409)
-12/25 M5*1 OK(409)
-12/28 M5*1 OK(409)
-1/4 M5*1 OK(409)
-1/14 M5*1 OK(409)
-1/16 M5*1 OK(409)
-1/23 M5*1 OK(410)
-1/26 M5*1 OK(410)
-3/26 M5*1 OK(410)
-4/9 M5*1 OK(410)
-4/12 M5*1 OK(410)
-4/16 M5*1 OK(410)
-4/19 M5*1 OK(410)
-5/17 M5*1 OK(410)
-8/13 M5*1 OK(813)
-8/21 M5*1 OK(813)
-8/29 M5*1 OK(813)
-10/22 M5*1 OK(410)
-10/30 M5*1 OK(410)
-11/6 M5*1 OK(410)
-2/14 M5*1 OK(410)
-5/15 M5*1 OK(410)
-5/22 M5*1 OK(410)
-5/28 M5*1 OK(410)
-8/14 M5*1 OK(410)
-10/28 M5*1 OK(410)
-11/4 M5*1 OK(410)
-11/19 M5*1 OK(410)
-12/17 M5*1 OK(410)
-12/24 M5*1 OK(410)
-12/30 M5*1 OK(410)
-21/7/9 M5*1 OK(410-H08000768)
-7/23 M5*1 OK(410-000400001184)
-7/29 M5*1 OK(410-000400001239)
-8/6 M5*1 OK(410-000400001265)
-8/13 M5*1 OK(410-000400001330)
-22/1/10 M5*1 OK(410-000400002041)
-1/19 M5*1 OK(410-000400001384)
-1/25 M5*1 OK(410-000400002120)
-3/4 M5*1 OK(410-000400002305)
-3/9 M5*1 OK(410-000400002082)
-3/14 M5*1 OK(410-000400002082)
-3/17 M5*1 OK(410-000400002250)
-4/7 M5*1 OK(410-000400002082)
-5/19 M5*1 OK(410-000400002082)
-24/5/27 M5*1 OK(410-000400004595)
-6/12 M5*1 OK(410-000400004595)
-7/3 M5*1 OK(410-000400004671)
-10/29 M5*1 OK(410-000400005054)
-25/2/8 M5*1 OK(410-000400005346)
-2/14 M5*1 OK(410-000400005346)
-3/10 M5*1 OK(410-000400005478)
-3/18 M5*1 OK(410-000400004671)
-7/10 M5*1 OK(410-000400005478)
-7/16 M5*1 OK(410-000400005404)
-7/24 M5*1 OK(410-000400005471)
-</t>
-      </text>
-    </comment>
-    <comment ref="G10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/24 出1台(三廠)
-5/10 出1台(三廠)
-5/11 出1台(三廠)
-6/4 出1台(三廠)
-6/12 出1台(三廠)
-6/22 出1台 (三廠)
-6/29 出1台 (三廠)
-7/3 研磨OK*1(7018)
-7/3 出1台 (三廠)
-7/6 出1台 (三廠)
-8/6 研磨OK*1(7018)
-8/10 出1台 (三廠)
-8/22 出1台 (三廠)
-8/29 出1台 (三廠)
-9/6 出1台 (三廠)
-9/19 出1台 (三廠)
-10/9 出1台 (三廠)
-10/15 研磨OK*1
-12/3 出1台 (三廠)
-12/22 出1台 (三廠-HA18090601)
-12/24 出1台 (三廠-HA18091001)
-1/8 研磨OK*1
-1/8 出1台 (三廠-HA18121201)
-1/10 研磨OK*1
-1/10 出1台 (三廠-HA18111901)
-1/22 研磨OK*1
-2/12 研磨OK*1
-2/15 出1台 (三廠-HA18122501)
-2/22 出1台 (三廠-HA19010402)
-3/6 研磨OK*1
-3/6 出1台 (三廠-HA19011401)
-2/26 研磨OK*1
-3/6 出1台 (三廠-HA19011602)
-3/14 研磨OK*1
-3/15 研磨OK*1
-3/27 出1台 (三廠-HA19012501)
-4/30 出1台 (三廠-HA19012301)
-5/24 研磨OK*1
-5/31 出1台 (三廠-HA19041201)
-6/6 研磨OK*1
-6/6 出1台 (三廠-HA19041602)
-6/19 研磨OK*1
-7/29 出1台 (三廠-HA19041902)
-8/8 研磨OK*1
-8/29 出1台 (三廠-HA19032602)
-9/4 研磨OK*1
-9/10 研磨OK*1
-9/18 研磨OK*1
-9/24 研磨OK*1
-10/23 出1台 (三廠-HA19082901)
-11/11 出1台 (三廠-HA19040901)
-11/19 出1台 (三廠-HA19051701)
-11/25 研磨OK*1
-11/28 研磨OK*1
-12/12 研磨OK*1
-1/3 出1台 (三廠-HA19081201)
-4/6 研磨OK*1
-4/13 出1台 (三廠-HA19082101-28059)
-4/17 出1台 (三廠-HA19110601-27007)
-4/29 出1台 (三廠-HA20021401-28062)
-4/23 研磨OK*1
-6/10 研磨OK*1
-7/7 出1台 (三廠-HA19103001-28131)
-7/7 研磨OK*1
-7/9 研磨OK*1
-8/18 出1台 (三廠-HA19102201-27770)
-8/28 出1台 (三廠-HA20052201-28262)
-9/9 出1台 (三廠-HA20052801-27835)
-11/5 出1台(三廠-HA20051501-機號:28335)
-11/9 研磨OK*1
-11/13 出1台(三廠-HA20081401-機號:28336)
-12/2 研磨OK*1
-12/3 出1台(三廠-HA20102901-機號:28291)
-12/3 研磨OK*1
-12/8 出1台(三廠-HA20110501-機號:27954)
-12/21 研磨OK*1
-21/1/13 出1台(三廠-HA20111901-機號:100000096)
-1/21 研磨OK*1
-2/20 研磨OK*1
-3/8 研磨OK*1
-3/16 出1台(三廠-HA20122401-機號:100000182)
-4/21 出1台(三廠-HA20121701-機號:100000424)
-7/14 出1台(三廠-HA20123001-100000554-H08000770)
-7/30 研磨OK*1
-8/2 出1台(三廠-HA21070901-100000468-H08000768)
-8/23 研磨OK*1(000400001184)
-8/31 研磨OK*1(000400001239)
-9/28 出1台(三廠-HA21072301-100001130-000400001184)
-9/24 研磨OK*1(000400001330)
-10/12 出1台(三廠-HA21081301-100000892-000400001330)
-10/14 出1台(三廠-HA21072801-100000816-000400001239)
-10/15 研磨OK*1(000400001265)
-22/4/19 研磨OK*2(000400002041，2082)
-4/20 研磨OK*1(000400002120)
-4/25 研磨OK*1(000400001384)
-7/6 出1台(三廠-HA21080601-100001891-000400001265)
-6/29 研磨OK*1(000400002082)
-8/9 出1台(三廠-HA22051901-100001968-000400002082)-100001737取消物料賢已吊走已扣除
-8/5 研磨OK*1(000400002082)-預計配#2493
-001289:
-12/5 研磨OK*1(000400002082)
-guang:
-23/1/9 研磨OK*1(000400002082)
-3/13 出1台(三廠-HA22030901-100002356-000400002082)
-3/24 研磨OK*1(000400002250)
-6/7 出1台(三廠-HA22031401-100002437-000400002082)
-guang:
-6/29 出1台(三廠-HA22012501-100002458-000400002120)
-7/20 出1台(三廠-HA22031701-100002411-000400002250)
-8/15 出1台(三廠-HA22011901-100002617-000400001384)
-8/15 研磨OK*1(000400002305)
-24/1/4 出1台(本廠-HA22011001-100002041-000400002616)
-4/2 出1台(三廠-HA22040701-100002493-000400002082)
-guang:
-4/11 出1台(三廠-HA22030401-100002829-000400002305)
-6/7 研磨OK*1(000400004595)
-6/11 出1台(三廠-HA24052701-100002761-000400004595)
-guang:
-6/20 研磨OK*1(000400004595)
-6/24 出1台(放裝三000400004595)(已入帳)
-guang:
-8/2 研磨OK*1(000400004671)
-11/4 出1台(放裝三000400004595)
-guang:
-11/11 出1台(三廠-HA24070301-100002948-000400004671)
-12/9 研磨OK*1(000400005054)
-12/16 出1台(三廠-HA24102901-100003035-000400005054)
-25/3/5 研磨OK*1(000400005346)
-3/20 研磨OK*1(000400005346)
-4/15 研磨OK*1(000400004671)
-4/21 研磨OK*1(000400005478)
-5/19 出1台(三廠-HA25021401-100003290-000400005346)
-8/7 研磨OK*1(000400005478)
-hsinwei:
-8/18 研磨OK*1(000400005471)
-9/4 研磨OK*1(000400005404)
-001280:  
-</t>
-      </text>
-    </comment>
-    <comment ref="J10" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
- 出1台(三廠-HA22040701-100002493-000400002082)
-</t>
-      </text>
-    </comment>
-    <comment ref="K10" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-2019/3/7入2支
-guang:
-3/15 出1支
-guang:
-6/17 NG*1(#4671-支撐機構破孔)
-guang:
-24/8/2 載走( LD-#4671)
-</t>
-      </text>
-    </comment>
-    <comment ref="L10" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-2019/3/7入2支
-guang:
-3/15 出1支
-</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-6/12 入1台(YZ)
-6/15 入1台(YZ)(NEW)
-6/16 入1台(YZ)(NEW)
-9/18 入1台(YZ)(NEW)
-9/28 入1台(YZ)(NEW)
-10/23 入1台(YZ)(NEW)
-10/30 入1台(YZ)(NEW)
-12/21 入1台(YZ)(NEW)
-4/16 入1台(YZ)(NEW)
-4/17 入1台(YZ)(NEW)
-5/8 入1台(YZ)(NEW)
-6/7 入1台(YZ)(NEW)
-6/12 入1台(YZ)(NEW)
-6/14 入1台(YZ)(NEW)
-7/26 入1台(YZ)(NEW)
-8/3 入1台(YZ)(NEW)
-8/29 入1台(YZ)(NEW)
-12/12 入1台(YZ)(NEW)
-1/2 入1台(YZ)(NEW)
-1/3 入1台(YZ)(NEW)
-1/7 入1台(YZ)(NEW)
-2/14 入1台(YZ)(NEW)
-2/15 入1台(YZ)(NEW)
-3/26 入1台(YZ)(NEW)
-3/28 入1台(YZ)(NEW)
-9/3 入2台(YZ)(NEW)
-12/2 入1台(YZ)(NEW)
-1/13 包砂*1(退回處理-YZ)
-1/15 入1台(處理完成-YZ)
-3/11 入1台(YZ)(NEW)
-3/26 入1台(YZ)(NEW)
-6/4 入1台(YZ)(NEW)
-6/29 入1台(YZ)(NEW)
-7/1 入1台(YZ)(NEW)
-7/6 入1台(YZ)(NEW)
-11/8 入1台(YZ)(NEW)
-11/15 入2台(YZ)(NEW)
-12/7 入1台(YZ-#2010)
-22/2/23 入1台(YZ-#2348)
-3/10 入1台(YZ-#2408)
-4/12 入1台(LD-#2348-換)
-5/3 入1台(LD-#2669)
-5/9 入1台(LD-#2614)
-5/16 入1台(LD-#2756)
-7/25 入1台(LD-#2973)
-8/31 入1台(LD-#2756-換)
-23/7/25 入1台(LD-#3722)
-8/9 入1台(LD-#3758)
-guang:
-24/5/8 入1台(LD-#3758-換)
-7/4 入1台(LD-#4778)
-12/4 入1台(LD-#5214)
-12/5 入1台(LD-#5264)
-12/10 入1台(LD-#5264)
-25/1/20 入1台(LD-#5393)
-3/4 入1台(LD-#5510)
-3/13 入1台(LD-#5525)
-6/4 入1台(LD-#5783)
-7/21 入1台(LD-#5864)
-12/8 入1台(LD-#6089)
-12/10 入2台(LD-#6090)
-26/1/7 入1台(LD-#6141)</t>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-7/24 M6*1 OK(17M)
-7/25 M6*1 OK(17M)
-7/26 M6*1 OK(17M)
-10/3 M6*1 OK(17M)
-10/27 M6*1 OK(17M)
-10/31 M6*1 OK(17M)
-11/9 M6*1 OK(17M)
-5/18 M6*1 OK(17M)
-5/19 M6*1 OK(17M)
-5/22 M6*1 OK(17M)
-7/2 M6*1 OK(17M)
-7/4 M6*1 OK(17M)
-8/16 M6*1 OK(17M)
-8/17 M6*1 OK(17M)
-8/20 M6*1 OK(17M)
-9/4 M6*1 OK(17M)
-10/2 M6*1 OK(17M)
-10/4 M6*1 OK(17M)
-10/25加工錯誤(M5-X偏10mm)
-4/12 M6*1 OK(17M)
-4/16 M6*1 OK(17M)
-6/17 M6*2 OK(408-M6-2)
-7/3 M6*3 OK(408-M6-2)
-11/19 M6*1 OK(409-M6-1)
-11/20 M6*1 OK(523-M6-2)
-11/25 M6*1 OK(17M)
-2/7 M6*1 OK(17M)
-4/16 M6*1 OK(17M.408)
-4/23 M6*1 OK(17M)
-7/14 M6*1 OK(17M)
-7/17 M6*1 OK(17M)
-7/23 M6*1 OK(17M)
-8/10 M6*1 OK(17M)
-11/19 M6*1 OK(17M-1907)-NG
-11/24 M6*1 OK(17M-1947)-NG
-12/13 M6*1 OK(17M-2010)
-12/21 M6*1 OK(17M-1947)
-22/1/17 入(磨開入料)OK
-5/16 M6*1 OK(17M-#2408)
-6/22 M6*1 OK(17M-#2348-換)
-8/5 M6*1 OK(17M-#2973)
-8/16 M6*1 OK(17M-#2614)
-8/30 M6*1 OK(17M-#2669)
-001289:
-11/29 M6*1 OK(17M-#2756)
-23/8/15 M6*1 OK(17M-#3758)
-guang:
-24/1/16 M6*1 OK(17M-#3722)
-5/22 M6*1 OK(17M-#3758-換)
-7/11 M6*1 OK(17M-#4778)
-12/6 M6*1 OK(17M-#5214)
-12/11 M6*1 OK(17M-#5214)
-12/13 M6*1 OK(17M-#5214)
-25/2/6 M6*1 OK(17M-#5393)
-3/13 M6*1 OK(17M-#5510)
-5/13 M6*1 OK(17M-#5525)
-6/20 M6*1 OK(17M-#5783)
-7/24 M6*1 OK(17M-#5864)
-12/11 M6*1 OK(17M-#6089)
-12/18 M6*1 OK(17M-#6090)
-12/23 M6*1 OK(17M-#6090)</t>
-      </text>
-    </comment>
-    <comment ref="F11" authorId="2" shapeId="0">
-      <text>
-        <t>ralf:
-支撐機構噴補X1待判 OK
-8/15 M5*1 OK(409)
-8/29 M5*1 OK(409)
-8/31 M5*1 OK(409)
-10/6 M5*1 OK(409)
-11/3 M5*1 OK(409)
-11/16 M5*1 OK(409)
-1/10 M5*1 OK(409)
-5/23 M5*1 OK(409)(5130L)
-5/25 M5*1 OK(409)(5130L)
-5/28 M5*1 OK(409)(5130L)
-7/9 M5*1 OK(409)(5130L)
-7/13 M5*1 OK(409)(5130L)
-8/27 M5*1 OK(409)(5130L)
-8/29 M5*1 OK(409)(5130L)
-8/31 M5*1 OK(409)(5130L)
-9/13 M5*1 OK(409)(5130L)
-10/17 M5*1 OK(409)(5130L)
-11/13 M5*1 OK(409)(5130L-線軌偏10mm)
-4/25 M5*1 OK(409)(5130L)
-5/2 M5*1 OK(409)(5130L)
-7/16 M5*1 OK(813)(5130L)
-7/18 M5*1 OK(410)(5130L)
-7/19 M5*1 OK(813)(5130L)
-7/24 M5*1 OK(410)(5130L)
-guang:
-8/1 M5*1 OK(410)(5130L)
-12/3 M5*1 OK(410)(5130L)
-12/12 M5*1 OK(410)(5130L)
-3/3 M5*1 OK(410)(5130L)
-4/28 M5*1 OK(410)(5130L)
-5/6 M5*1 OK(410)(5130L)
-8/21 M5*1 OK(410)(5130L)
-8/28 M5*1 OK(410)(5130L)
-9/4 M5*1 OK(410)(5130L)
-9/10 M5*1 OK(410)(5130L)
-12/13 M5*1 NG(410-砂孔)-#1907
-12/15 M5*1 NG(410-砂孔)-#1947
-12/16 載回1台(M5B270包砂-NG-#1907
-22/1/14 載回1台(M5B270包砂-NG-#1947
-2/7 M5*1 OK(410-#1947)(5130L)
-2/12 M5*1 OK(410-#2010)(5130L)
-3/23 M5*1 OK(410-#1947)(5130L)
-5/24 M5*1 OK(410-#2408)(5130L)
-8/12 M5*1 OK(410-#2348)(5130L)
-8/17 M5*1 OK(410-#2973)(5130L)
-9/12 M5*1 OK(410-#2614)(5130L)
-10/18 M5*1 OK(410-#2669)(5130L)
-001289:
-12/8 M5*1 OK(410-#2756)(5130L)
-guang:
-24/3/26 M5*1 OK(410-#3722)(5130L)
-6/4 M5*1 OK(410-#3758)(5130L)
-7/17 M5*1 OK(410-#4778)(5130L)
-12/16 M5*1 OK(410-#5214)(5130L)
-12/23 M5*1 OK(410-#5264)(5130L)
-12/31 M5*1 OK(410-#5264)(5130L)
-25/2/21 M5*1 OK(410-#5393)(5130L)
-3/27 M5*1 OK(410-#5510)(5130L)
-6/20 M5*1 OK(410-#5525)(5130L)
-7/4 M5*1 OK(410-#5783)(5130L)
-8/14 M5*1 OK(410-#5864)(5130L)
-12/18 M5*1 OK(410-#6089)(5130L)
-12/26 M5*1 OK(410-#6090)(5130L)
-26/1/5 M5*1 OK(410-#6090)(5130L)</t>
-      </text>
-    </comment>
-    <comment ref="G11" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-11/1 研磨OK*1
-1/5 出1台(三廠)
-1/11 出1台(三廠)
-2/14 出1台(三廠)
-2/22 出1台(三廠)
-3/21 出1台(三廠)
-4/27 出1台(三廠)
-7/13 出1台(三廠)
-7/17 出1台(三廠)
-8/15 出1台(三廠)
-8/17 出1台(三廠)
-9/10 出1台(三廠)
-102  研*1 OK
-11/01 出1台(三廠)
-11/15 研磨OK*1
-11/20 研磨OK*1(光學尺)
-11/20 出1台(三廠)(光學尺)
-3/14 出1台(三廠-HA18070901)
-3/18 研磨OK*1
-3/18 出1台(三廠-HA18101702)
-3/20 出1台(三廠-HA18082801)
-4/19 出1台(三廠-HA18111301)
-4/17 研磨OK*1
-4/23 出1台(三廠-HA18011002-5BC)
-5/10 研磨OK*1
-6/28 出1台(三廠-HA18091201)
-7/9 研磨OK*1
-7/10 出1台(三廠-HA19050201)
-7/17 研磨OK*1
-7/31 出1台(三廠-HA19042401)
-7/16 研磨OK*1(退磨-已開單)
-8/20 研磨OK*1
-8/20 出1台(三廠-HA19071802)
-8/22 研磨OK*1
-8/26 研磨OK*1
-8/27 研磨OK*1
-9/9 出1台(三廠-HA19071801)
-9/30 出1台(三廠-HA19072401)
-10/22 研磨OK*1
-2/3 出1台(三廠-HA19080101)
-2/11 出1台(三廠-HA19071901)
-2/14 研磨OK*1
-2/14 出1台(三廠-HA19120301)
-2/25 研磨OK*1
-3/13 出1台(三廠-HA15031301-退磨-已開單)
-3/20 出1台(三廠-HA19121201)
-4/9 研磨OK*1
-6/3 研磨OK*1
-8/11 研磨OK*1
-10/27 研磨OK*2
-10/29 研磨OK*1
-21/5/24 出1台(三廠-HA20090401-100000645)
-6/2 出1台(三廠-HA20050601-100000712)
-7/28 出1台(三廠-HA20042801-100000742)
-9/6 出1台(三廠-HA20082801-100000587)
-10/12 出1台(三廠-HA20091001-100000817-000400001776)
-12/8 研磨OK*1
-22/1/22 出1台(三廠-HA20082101-100001255-000400001776)
-2/8 出1台(三廠-HA20030301-100000955-000400001776)
-3/15 研磨OK*2(#1947,#2010)
-5/13 研磨OK*1(#1947)
-6/29 研磨OK*1(#2408)
-7/15 出1台(三廠-HA22021201-100001931-000400002010)
-10/31 出1台(三廠-HA22032301-100001823-000400001947)
-001289:
-11/10 研磨OK*1(#2614)
-guang:
-12/5 出1台(三廠-HA22091201-100002145-000400002614)
-23/2/20 出1台(三廠-HA22020701-100002221-000400001947)
-3/21 出1台(三廠-HA22052401-100002220-000400002408)
-4/11 研磨OK*1(#2348)
-4/14 出1台(三廠-HA23041101-100002302-000400002348)
-5/8 研磨OK*1(#2669)
-5/10 研磨OK*1(#2973)
-5/15 研磨OK*1(#2756)
-5/18 出1台(三廠-HA22101801-100002297-000400002669)
-6/8 出1台(三廠-HA22081701-100002254-000400002973)
-9/25 出1台(三廠-HA22120801-100002465-000400002756)
-24/5/8 研磨OK*1(#3722)
-5/29 出1台(三廠-HA24032601-100002804-000400003722)
-6/14 研磨OK*1(#3758)
-6/17 出1台(三廠-HA24060401-100002805-000400003758)
-7/23 研磨OK*1(#4778)
-7/23 出1台(三廠-HA24071701-100002834-000400004778)
-25/1/2 研磨OK*1(#5214)
-1/6 出1台(三廠-HA24121401-100003051-000400005214)
-1/13 研磨OK*1(#5264)
-1/24 出1台(三廠-HA24122301-100003089-000400005264)
-2/6 研磨OK*1(#5264)
-3/24 出1台(三廠-HA24123101-100003185-000400005264)
-3/31 研磨OK*1(#5393)
-guang:
-4/18 出1台(三廠-HA25022101-100003186-000400005393)(轉去100003320-HSA627EAY使用)
-5/8 研磨OK*1(#5510)
-6/16 出1台(三廠-HA25032701-100003310-000400005510)
-7/4 研磨OK*1(#5525)
-8/12 研磨OK*1(#5783)
-hsinwei:
-9/4出1台(三廠-HA25070401-100003314-000400005783)
-001280
-9/9 研磨OK*1(#5864)
-11/20 出1台(三廠-HA25062001-100003370-000400005525)
-12/2 出1台(三廠-HA25081301-100003407-000400005864)
-12/29 研磨OK*1(#6089)
-26/1/5 出1台(三廠-HA25121801-100003410-000400006089)
-1/8 研磨OK*1(#6090)
-1/9 出1台(三廠-HA25122601-100003446-000400006090)</t>
-      </text>
-    </comment>
-    <comment ref="K11" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-22/3/2 M6*1 NG(#2348-M6包砂)
-3/28 出1台( LD載走-#2348)
-5/27 M6*1 NG(#2756-M6包砂)
-6/7 出1台( LD載走-#2756)
-guang:
-23/8/10 M6*1 NG(#3722-M6包砂-救援成功)
-10/2 M5*1 NG(#3758-結合面孔內包砂)
-guang:
-24/5/6 出1台( LD載走-#3758)
-</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-11/29 楊鋼入1
-9/27 楊鋼入1
-10/23 入1PS(YK)
-5/21 入1台(YK)(NEW)
-6/15 入1台(YK)(NEW)
-1/8 入1台(YK)(NEW)
-1/30 入1台(YK)(NEW)
-1/31 入1台(YK)(NEW)
-2/22 入1台(YK)(NEW)
-10/29 入1台(YK)(NEW)
-11/16 入1台(YK)(NEW)
-21/4/28 入2台(YK)(NEW)
-6/17 入2台(YK)(NEW)
-7/14 入1台(YK)(NEW)
-11/3 入1台(YK-1064)(補件)
-22/2/18 入1台(YK-718)(補件)
-</t>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-6/1 M6*1 OK(17M)
-10/17 M6*1 OK(17M)
-11/10 M6*1 OK(17M)
-10/24 M6*1 OK(17M)
-10/25 M6*1 OK(17M)
-1/24 M6*1 OK(17M)
-2/19 M6*1 OK(17M)
-2/20 M6*1 OK(17M)
-11/6 M6*1 OK(17M)
-11/4 M6*1 OK(17M)
-11/20 M6*1 OK(17M)
-21/5/19 M6*1 OK(17M)
-5/21 M6*1 OK(17M)
-7/21 M6*1 OK(17M-718)
-7/28 M6*1 OK(17M-1064)-砂孔報廢*1
-8/30 出1台( YK-載回-砂孔-1064)
-12/30 M6*1 OK(17M-#1064)
-22/6/9 M6*1 OK(17M-#718-補件)
-</t>
-      </text>
-    </comment>
-    <comment ref="F12" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-6/6 M5*1 OK(410)
-10/26 M5*1 OK(410)
-1/4 M5*1 OK(409)
-11/8 M5*1 OK(409)
-12/07 M5*1 OK(409)
-1/31 M5*1 OK(410)
-2/26 M5*1 OK(410)
-3/5 M5*1 OK(410)
-11/19 M5*1 OK(410)
-11/13 M5*1 OK(410)
-12/4 M5*1 OK(410)
-21/5/27 M5*1 OK(410-H08000801)
-6/1 M5*1 OK(410-H08000801)
-10/7 M5*1 OK(410-000400001064)
-9/24 出1台( YK-載回-結合面包砂-718)
-22/1/14 M5*1 OK(410-000400001064)
-10/11 M5*1 OK(410-000400000718)
-</t>
-      </text>
-    </comment>
-    <comment ref="G12" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-1/4出1PS
-1/19出1PSralf:
-6/23 研磨OK*1(7018)
-7/21 出1台
-3/29 出1台(3廠)
-12/6 研磨OK*1
-12/22 出1台(3廠-HA18010402)
-1/2 出1台(3廠-HA17102602)
-1/3 研磨OK*1
-1/17 出2台(3廠-HA18110801,18120701)
-1/3 研磨OK*1
-2/23 出1台(3廠-HA19013101)
-3/18 研磨OK*1
-3/20 研磨OK*1
-4/10 出1台(3廠-HA19030501)
-11/29 出1台(3廠-HA1902601)
-1/15 研磨OK*1
-8/13 出1台(3廠-HA19111901-機號:28232)
-11/30 研磨OK*1
-12/1 出1台(3廠-HA20111301-機號:28328)
-2021/1/4 研磨OK*1
-1/4 出1台(3廠-HA20120401-機號:28339)
-6/16 研磨OK*1(H08000801)
-7/26 研磨OK*1(H08000801)
-22/5/11 研磨OK*1(000400001064)
-6/8 出1台(3廠-HA21060101-100001744-H08000801)
-23/4/14 研磨OK*1(000400000718)
-7/7 出1台(3廠-HA21052701-100002466-H08000801)
-22/1/18 研磨OK*1(000400001064)
-25/4/18 出1台(3廠-HA22101101-100003172-000400000718)
-</t>
-      </text>
-    </comment>
-    <comment ref="C13" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-11/13 入2台(加政轉)(OLD)
-3/20 入1台(YK)(OLD)
-3/22 入1台(YK)(OLD)
-3/26 入1台(YK)(OLD)
-3/30 入1台(YK)(OLD)
-4/10 入1台(YK)(OLD)
-guang:
-4/11 出2台(轉加政加工                   5/2 入1台(YK)(OLD)
-6/15 入1台(YK)(OLD)
-guang:
-24/9/11 入1台(YK-#4975)
-入錯料-9/23 加工發現
-9/24 出1台(YK-#4975-送錯機型)
-10/22 入1台(YK-#4975)-換
-guang:
-</t>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-11/15 M6*1 OK(17M)
-11/17 M6*1 OK(17M)
-5/24 M6*1 OK(17M)
-6/25 M6*1 OK(17M)
-7/5 M6*1 OK(17M)
-10/26 M6*1 OK(17M)
-10/31 M6*1 OK(17M)
-guang:
-24/10/25 M6*1 OK(17M-#4975)
-</t>
-      </text>
-    </comment>
-    <comment ref="F13" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-11/24 M5*1 OK(409)
-1/8 M5*1 OK(409)
-5/31 M5*1 OK(409)-H08000803
-7/3 M5*1 OK(409)-H08000803
-7/17 M5*1 OK(409)-H08000803
-11/7 M5*1 OK(813)
-12/19 M5*1 OK(409)
-guang:
-24/11/28 M5*1 OK(410-#4975-OLD版)
-</t>
-      </text>
-    </comment>
-    <comment ref="G13" authorId="0" shapeId="0">
-      <text>
-        <t>guang:
-1/30 出1台(三廠)
-3/31 出1台(三廠)
-6/21 出1台(三廠)
-10/19 研*1 OK-H08000803
-5/7 研*1 OK-H08000803
-9/2 研*1 OK-H08000803
-21/5/13 出1台(三廠-HA18121901-100000590)
-23/8/7 出1台(三廠-HA18110701-100002490)
-9/14 出1台(三廠-HA18053101-H08000803-100002503)
-guang:
-24/7/11  出1台(三廠-HA18070301-100002841-#4764)(H08000803)
-11/4  出1台(三廠-HA18071702-100002929-#5108)(H08000803)
-25/5/28 研*1 OK-(000400004975)
-11/4  出1台(三廠-HA24112701-100003360-#4975)</t>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/10 入1台(YZ)(特殊6550L)
-3/13 入1台(YZ)
-4/13 永棧入1
-4/28 入1台(YZ)
-7/14 入1台(YZ)(NEW)
-8/17 入1台(YZ)(NEW)
-guang:
-8/28 入1台(YZ)(NEW)
-9/4 入1台(YZ)(NEW)
-11/20 入1台(YZ)(特殊6550L)(NEW)
-11/24 入1台(YZ)(NEW)
-12/5入1台(YZ)(NEW)
-12/18入1台(YZ)(NEW)
-12/19入1台(YZ)(NEW)
-1/18入1台(YZ)(NEW)
-1/23入1台(YZ)(NEW)
-1/31入1台(YZ)(NEW)
-3/20 入1台(YZ)(NEW)
-4/2 出2台(轉隆升加工)
-4/9 出3台(轉隆升加工)
-guang:
-22/6/20 入1台(LD-#2873)
-7/1 入1台(LD-#2873)
-8/19 入1台(LD-#3064)(2)
-9/2 入1台(LD-#3064)
-25/9/1 入1台(LD-#5951)
-</t>
-      </text>
-    </comment>
-    <comment ref="E14" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/22 M6*1 OK(特殊6550L)
-4/14 M6*1OK (17m)
-5/19 M6*1OK (17m)
-7/18 M6*1OK (17m)
-8/22 M6*1OK (17m)
-9/6 M6*1OK(17M)
-9/12 M6*1OK(17M)
-12/7 M6*1 OK(17M)
-12/9 M6*1 OK(17M)
-3/30 M6*1 OK(17M)
-22/6/25 M6*1 OK(17M-#2873)
-7/12 M6*1 OK(17M-#2873)
-8/26 M6*1 OK(17M-#3064)
-9/12 M6*1 OK(17M-#3064)
-25/9/5 M6*1 OK(17M-#5951)
-</t>
-      </text>
-    </comment>
-    <comment ref="F14" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/30 M5*1 OK(特殊6550L)
-4/25 M5*1 OK(410)
-6/1 M5*1 OK(410)
-7/24 M5*1 OK(409)
-7/25 M5*1 OK(409)
-9/16 M5*1 OK(409)
-9/20 M5*1 OK(409)
-12/12 M5*1 OK(409)
-12/15 M5*1 OK(813)
-4/13 M5*1 OK(409)
-22/7/1 M5*1 OK(410-#2873)
-7/18 M5*1 OK(410-#2873)
-9/2 M5*1 OK(410-#3064)
-9/22 M5*1 OK(410-#3064)
-25/9/18 M5*1 OK(410-#5951)
-</t>
-      </text>
-    </comment>
-    <comment ref="G14" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-3/7出1台ralf:
-5/9 研磨*1 OK(6550L)特殊
-5/23 研磨OK*1(7018)
-5/25 出1台
-ralf:
-6/5 研磨OK*1(7018)
-guang:
-6/5 出1台
-ralf:
-7/14 研磨OK*1
-8/16 研磨OK*1
-8/17 出1台
-9/1 出1台
-9/7 出1台
-ralf:
-10/3 研磨OK*1
-guang:
-10/11 出1台
-10/20 出1台
-12/19 出1台
-5/16 出1台(三廠)
-guang:
-11/20 出1台(三廠-CL18053001-機號:27309)
-guang:
-21/11/25 出1台(隆升加工-000400000917
-22/1/22 出1台(隆升加工-100001093
-4/7 出1台(隆升加工-100001545)
-hsin:
-6/13 出1台(三廠機號:100001735)
-guang:
-22/712 研磨*1(000400002873)
-7/14 出1台(三廠-HA22070101-100001755-000400002873)
-9/5 研磨*1(000400002873)
-9/5 出1台(三廠-HA22071801-100001903-000400002873)
-10/6 研磨*1(000400003064)
-guang:
-23/4/13 研磨*1(000400003064)
-12/11 出1台(三廠-HA22090201-100002358-000400003064)
-24/3/20 出1台(三廠-HA22092201-100002688-000400003064)
-hsinwei:
-25/10/8 研磨*1(000400005951)
-10/8 出1台(三廠-HA25091801-100003325-000400005951)
-</t>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/16 入1台(YZ)(NEW)
-5/11 入1台(YZ)(NEW)
-6/11 入1台(YZ)(NEW)
-8/1 入1台(JS)(NEW)
-8/9 入2台(JS)(NEW)
-8/17 入1台(YZ)(NEW)
-8/23 入1台(JS)(NEW)
-10/16 入1台(JS)(NEW)
-10/22 入1台(JS)(NEW)
-8/21 入1台(YZ)(NEW)
-8/24 入1台(YZ)(NEW)
-11/6 入1台(YZ)(NEW)
-11/13 入1台(YZ)(NEW)
-21/7/12 入1台(JS)(NEW)
-7/19 入1台(JS)(NEW)
-</t>
-      </text>
-    </comment>
-    <comment ref="E15" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-8/14 M6*1 OK(17M)
-11/21M6*1 OK(17M)
-6/7 M6*1 OK(17M)
-6/8 M6*1 OK(17M)
-7/17 M6*1 OK(17M)
-9/11 M6*1 OK(17M)
-9/12 M6*1 OK(17M)
-9/13 M6*1 OK(17M)
-10/22 M6*1 OK(17M)
-10/24 M6*1 OK(17M)
-11/27 M6*1 OK(17M)
-12/3 M6*1 OK(17M)
-12/5 M6*1 OK(17M)
-8/27 M6*1 OK(17M)(標準機用)
-10/15 M6*1 OK(17M)
-12/31 M6*1 OK(17M)
-21/1/5 M6*1 OK(17M)
-9/3 M6*1 OK(17M-464)
-9/7 M6*1 OK(17M-464)
-</t>
-      </text>
-    </comment>
-    <comment ref="F15" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-4/27 M5*1 OK(410)
-10/18 M5*1 OK(410)
-5/2 M5*1 OK(410)
-6/12 M5*1 OK(409)
-6/14 M5*1 OK(409)
-ralf:
-7/2 1支背部砂孔報廢
-guang:
-7/5 出1台(裂痕-報廢)
-7/28 M5*1 OK(409)
-9/15 M5*1 OK(409)
-9/19 M5*1 OK(409)
-9/21 M5*1 OK(409)
-11/8 M5*1 OK(813)
-11/19 M5*1 OK(813)
-12/19 M5*1 OK(813)
-12/27 M5*1 OK(813)
-2/6 M5*1 OK(813)
-10/15 M5*1 OK(813)
-10/23 M5*1 OK(813)(配EA/EAY)
-21/1/27 M5*1 OK(410)
-2/4 M5*1 OK(410)
-10/22 M5*1 OK(410-000400000464-JS)
-10/29 M5*1 OK(410-000400000464-JS)
-</t>
-      </text>
-    </comment>
-    <comment ref="G15" authorId="2" shapeId="0">
-      <text>
-        <t xml:space="preserve">ralf:
-6/9 研磨OK*1(7018)
-11/2 出1台(3廠)
-5/2 出1台(3廠)
-5/7 出1台(3廠)
-7/17 出1台(3廠)
-7/25 出1台(3廠)
-10/26 研磨OK*1
-11/19 研磨OK*1
-2/21 出1台(3廠-HA18092102)
-4/1 出1台(3廠-HA18072801)
-9/16 出1台(3廠-HA18091501)
-10/2 研磨OK*1
-10/3 出1台(3廠-HA18091902)
-12/27 研磨OK*1
-2/15 研磨OK*1
-2/18 研磨OK*1
-10/3 出1台(3廠-HA19110801-台鐵用-27930)
-4/21 研磨OK*1
-5/6 出1台(3廠-HA19121901-28076)
-5/8 出1台(3廠-HA20020601-26808)
-5/12 研磨OK*1(標準機用)
-7/21 出1台(3廠-HA19122701-28190)
-21/1/28 研磨OK*1
-2/24 出1台(3廠-HA19111901-100000018)
-6/4 研磨OK*1
-6/8 研磨OK*1
-22/7/11 研磨OK*1(000400000464)
-10/6 研磨OK*1(000400000464)
-23/11/28 出1台(3廠-HA21102201-100002515-000400000464)
-24/1/25 研磨OK*1(無編號)
-</t>
-      </text>
-    </comment>
-    <comment ref="C16" authorId="3" shapeId="0">
-      <text>
-        <t xml:space="preserve">001289:
-11/1 入2台(SY-#3124)
-guang:
-24/2/29 入1台(SY-#4359)
-</t>
-      </text>
-    </comment>
-    <comment ref="E16" authorId="3" shapeId="0">
-      <text>
-        <t xml:space="preserve">001289:
-11/11 M6*1 OK(409)
-11/15 M6*1 OK(409)
-guang:
-24/3/6 M6*1 OK(410-#4359)
-24/3/9 M6*1 OK(410-#4359)
-</t>
-      </text>
-    </comment>
-    <comment ref="F16" authorId="3" shapeId="0">
-      <text>
-        <t xml:space="preserve">001289:
-11/21 M5*1 OK(410-#3124)
-11/23 M5*1 OK(410-#3124)
-guang:
-23/5/24 出*2台(元榮研-#3124)
-24/3/13 M5*1 OK(410-#4359)
-3/21 出1台(元榮-HA24031301-100002726-#4359)
-</t>
-      </text>
-    </comment>
-    <comment ref="C17" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/11/6 入1台(YJF-#4023)
-guang:
-</t>
-      </text>
-    </comment>
-    <comment ref="D17" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/11/8 M7*1 OK(813-#4023)
-</t>
-      </text>
-    </comment>
-    <comment ref="E17" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/11/13 M6*1 OK(813-#4023)
-</t>
-      </text>
-    </comment>
-    <comment ref="F17" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/11/27 M5*1 OK(410-#4023)
-11/28 出*1台(台典研-100002659#4023)
-guang:
-</t>
-      </text>
-    </comment>
-    <comment ref="C18" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/12/4 入1台(LD-#4092)
-</t>
-      </text>
-    </comment>
-    <comment ref="D18" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/12/12 M7*1 OK(813-#4092)
-</t>
-      </text>
-    </comment>
-    <comment ref="E18" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/12/14 M6*1 OK(813-#4092)
-</t>
-      </text>
-    </comment>
-    <comment ref="F18" authorId="0" shapeId="0">
-      <text>
-        <t xml:space="preserve">guang:
-23/12/26 M5*1 OK(410-#4092)
-12/27 出1台(台典研-#4092)
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>guang</author>
     <author>ralf</author>
   </authors>
   <commentList>
@@ -3775,7 +1180,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>ralf</author>
@@ -3792,7 +1197,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>guang</author>
@@ -3808,7 +1213,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>guang</author>
@@ -11078,7 +8483,7 @@
         </is>
       </c>
       <c r="C2" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="53" t="n">
         <v>0</v>
@@ -11091,7 +8496,7 @@
       </c>
       <c r="G2" s="53" t="inlineStr"/>
       <c r="H2" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="53" t="inlineStr"/>
       <c r="J2" s="53" t="inlineStr"/>
@@ -11150,13 +8555,15 @@
         <v>0</v>
       </c>
       <c r="E4" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="53" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="53" t="inlineStr"/>
-      <c r="H4" s="53" t="inlineStr"/>
+      <c r="H4" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="I4" s="53" t="inlineStr"/>
       <c r="J4" s="53" t="inlineStr"/>
       <c r="K4" s="53" t="inlineStr"/>
@@ -11441,13 +8848,15 @@
         <v>0</v>
       </c>
       <c r="E13" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" s="53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G13" s="53" t="inlineStr"/>
-      <c r="H13" s="53" t="inlineStr"/>
+      <c r="H13" s="53" t="n">
+        <v>4</v>
+      </c>
       <c r="I13" s="53" t="inlineStr"/>
       <c r="J13" s="53" t="inlineStr"/>
       <c r="K13" s="53" t="n">
@@ -11787,10 +9196,10 @@
         <v>1</v>
       </c>
       <c r="E23" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="F23" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="G23" s="53" t="inlineStr"/>
       <c r="H23" s="53" t="n">
@@ -11863,14 +9272,14 @@
         <v>0</v>
       </c>
       <c r="E25" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" s="53" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="53" t="inlineStr"/>
       <c r="H25" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="53" t="inlineStr"/>
       <c r="J25" s="53" t="inlineStr"/>
@@ -11964,16 +9373,16 @@
         </is>
       </c>
       <c r="C28" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="D28" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="G28" s="53" t="inlineStr"/>
       <c r="H28" s="53" t="n">
@@ -12044,7 +9453,7 @@
         </is>
       </c>
       <c r="C30" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" s="53" t="n">
         <v>0</v>
@@ -12484,13 +9893,13 @@
         </is>
       </c>
       <c r="C44" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="53" t="n">
         <v>1</v>
-      </c>
-      <c r="D44" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="F44" s="53" t="n">
         <v>0</v>
@@ -12693,7 +10102,7 @@
         <v>2</v>
       </c>
       <c r="D50" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E50" s="53" t="n">
         <v>0</v>
@@ -12702,7 +10111,9 @@
         <v>0</v>
       </c>
       <c r="G50" s="53" t="inlineStr"/>
-      <c r="H50" s="53" t="inlineStr"/>
+      <c r="H50" s="53" t="n">
+        <v>3</v>
+      </c>
       <c r="I50" s="53" t="inlineStr"/>
       <c r="J50" s="53" t="n">
         <v>1</v>
@@ -12859,14 +10270,14 @@
         <v>0</v>
       </c>
       <c r="E55" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55" s="53" t="n">
         <v>0</v>
       </c>
       <c r="G55" s="53" t="inlineStr"/>
       <c r="H55" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" s="53" t="inlineStr"/>
       <c r="J55" s="53" t="inlineStr"/>
@@ -13055,13 +10466,13 @@
         </is>
       </c>
       <c r="C61" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" s="53" t="n">
         <v>0</v>
       </c>
       <c r="E61" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="53" t="n">
         <v>1</v>
@@ -13161,10 +10572,12 @@
         <v>0</v>
       </c>
       <c r="F64" s="53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G64" s="53" t="inlineStr"/>
-      <c r="H64" s="53" t="inlineStr"/>
+      <c r="H64" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="I64" s="53" t="inlineStr"/>
       <c r="J64" s="53" t="inlineStr"/>
       <c r="K64" s="53" t="inlineStr"/>
@@ -13759,13 +11172,19 @@
       <c r="E9" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="53" t="inlineStr"/>
-      <c r="G9" s="53" t="inlineStr"/>
+      <c r="F9" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="H9" s="53" t="n">
         <v>1</v>
       </c>
       <c r="I9" s="53" t="inlineStr"/>
-      <c r="J9" s="53" t="inlineStr"/>
+      <c r="J9" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" s="53" t="n">
         <v>0</v>
       </c>
@@ -13891,7 +11310,7 @@
         </is>
       </c>
       <c r="C13" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" s="53" t="n">
         <v>0</v>
@@ -13906,7 +11325,7 @@
         <v>0</v>
       </c>
       <c r="H13" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" s="53" t="inlineStr"/>
       <c r="J13" s="53" t="n">
@@ -14006,7 +11425,7 @@
         </is>
       </c>
       <c r="C16" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="53" t="n">
         <v>1</v>
@@ -14025,7 +11444,7 @@
       </c>
       <c r="I16" s="53" t="inlineStr"/>
       <c r="J16" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" s="53" t="inlineStr"/>
       <c r="L16" s="53" t="inlineStr"/>
@@ -14422,11 +11841,11 @@
         <v>0</v>
       </c>
       <c r="H27" s="53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="53" t="inlineStr"/>
       <c r="J27" s="53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" s="53" t="inlineStr"/>
       <c r="L27" s="53" t="n">
@@ -14838,7 +12257,7 @@
         </is>
       </c>
       <c r="C38" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" s="53" t="n">
         <v>0</v>
@@ -14857,7 +12276,7 @@
       </c>
       <c r="I38" s="53" t="inlineStr"/>
       <c r="J38" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" s="53" t="inlineStr"/>
       <c r="L38" s="53" t="inlineStr"/>
@@ -14889,13 +12308,19 @@
       <c r="E39" s="53" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="53" t="inlineStr"/>
-      <c r="G39" s="53" t="inlineStr"/>
+      <c r="F39" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="53" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="53" t="inlineStr"/>
-      <c r="J39" s="53" t="inlineStr"/>
+      <c r="J39" s="53" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" s="53" t="inlineStr"/>
       <c r="L39" s="53" t="inlineStr"/>
       <c r="M39" s="53" t="inlineStr"/>
@@ -14912,290 +12337,283 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor indexed="61"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
-  <cols>
-    <col width="24.625" customWidth="1" style="90" min="1" max="1"/>
-    <col width="22.25" customWidth="1" style="90" min="2" max="2"/>
-    <col width="11.75" customWidth="1" style="90" min="6" max="6"/>
-    <col width="12.125" customWidth="1" style="90" min="7" max="8"/>
-    <col width="13.25" customWidth="1" style="90" min="10" max="10"/>
-    <col width="18" customWidth="1" style="53" min="11" max="11"/>
-    <col width="18" customWidth="1" style="90" min="12" max="12"/>
-    <col width="23.25" customWidth="1" style="90" min="14" max="14"/>
-    <col width="18.875" customWidth="1" style="90" min="15" max="15"/>
-    <col width="33.25" customWidth="1" style="90" min="16" max="16"/>
-  </cols>
+  <dimension ref="A1:P18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="54" t="inlineStr">
+      <c r="A1" s="111" t="inlineStr">
         <is>
           <t>品號</t>
         </is>
       </c>
-      <c r="B1" s="54" t="inlineStr">
+      <c r="B1" s="111" t="inlineStr">
         <is>
           <t>機型</t>
         </is>
       </c>
-      <c r="C1" s="54" t="inlineStr">
+      <c r="C1" s="111" t="inlineStr">
         <is>
           <t>素材</t>
         </is>
       </c>
-      <c r="D1" s="54" t="inlineStr">
+      <c r="D1" s="111" t="inlineStr">
         <is>
           <t>製程7</t>
         </is>
       </c>
-      <c r="E1" s="54" t="inlineStr">
+      <c r="E1" s="111" t="inlineStr">
         <is>
           <t>製程6</t>
         </is>
       </c>
-      <c r="F1" s="54" t="inlineStr">
+      <c r="F1" s="111" t="inlineStr">
         <is>
           <t>製程5(成品)</t>
         </is>
       </c>
-      <c r="G1" s="54" t="inlineStr">
+      <c r="G1" s="111" t="inlineStr">
         <is>
           <t>研磨成品</t>
         </is>
       </c>
-      <c r="H1" s="83" t="inlineStr">
+      <c r="H1" s="111" t="inlineStr">
         <is>
           <t>報廢品</t>
         </is>
       </c>
-      <c r="I1" s="54" t="inlineStr">
+      <c r="I1" s="111" t="inlineStr">
         <is>
           <t>總數</t>
         </is>
       </c>
-      <c r="J1" s="83" t="inlineStr">
+      <c r="J1" s="111" t="inlineStr">
         <is>
           <t>預扣件</t>
         </is>
       </c>
-      <c r="K1" s="83" t="inlineStr">
-        <is>
-          <t>報廢品</t>
-        </is>
-      </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="K1" s="111" t="inlineStr">
+        <is>
+          <t>報廢品.1</t>
+        </is>
+      </c>
+      <c r="L1" s="111" t="inlineStr">
+        <is>
+          <t>Unnamed: 11</t>
+        </is>
+      </c>
+      <c r="M1" s="111" t="inlineStr">
         <is>
           <t>研-09-09</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="N1" s="111" t="inlineStr">
+        <is>
+          <t>Unnamed: 13</t>
+        </is>
+      </c>
+      <c r="O1" s="111" t="inlineStr">
+        <is>
+          <t>Unnamed: 14</t>
+        </is>
+      </c>
+      <c r="P1" s="111" t="inlineStr">
         <is>
           <t>已開單</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="83" t="n">
+      <c r="A2" s="53" t="n">
         <v>8817000571</v>
       </c>
-      <c r="B2" s="72" t="inlineStr">
+      <c r="B2" s="53" t="inlineStr">
         <is>
           <t>AHC-X31</t>
         </is>
       </c>
-      <c r="C2" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="83" t="n"/>
-      <c r="E2" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" s="83" t="n"/>
-      <c r="I2" s="83">
-        <f>SUM(C2:H2)</f>
-        <v/>
-      </c>
-      <c r="J2" s="61" t="n"/>
-      <c r="K2" s="9" t="n"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="C2" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="53" t="inlineStr"/>
+      <c r="E2" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="53" t="inlineStr"/>
+      <c r="I2" s="53" t="inlineStr"/>
+      <c r="J2" s="53" t="inlineStr"/>
+      <c r="K2" s="53" t="inlineStr"/>
+      <c r="L2" s="53" t="inlineStr">
         <is>
           <t>5270L</t>
         </is>
       </c>
-      <c r="M2" s="9" t="n"/>
-      <c r="N2" s="72" t="inlineStr">
+      <c r="M2" s="53" t="inlineStr"/>
+      <c r="N2" s="53" t="inlineStr">
         <is>
           <t>AHC-X31</t>
         </is>
       </c>
-      <c r="P2" s="9" t="n"/>
+      <c r="O2" s="53" t="inlineStr"/>
+      <c r="P2" s="53" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="83" t="n">
+      <c r="A3" s="53" t="n">
         <v>8817000566</v>
       </c>
-      <c r="B3" s="72" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>AHC-X36</t>
         </is>
       </c>
-      <c r="C3" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="83" t="n"/>
-      <c r="E3" s="83" t="n">
+      <c r="C3" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="53" t="inlineStr"/>
+      <c r="E3" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="F3" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="83" t="n">
+      <c r="F3" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="83" t="n"/>
-      <c r="I3" s="84">
-        <f>SUM(C3:G3)</f>
-        <v/>
-      </c>
-      <c r="J3" s="62" t="n"/>
-      <c r="K3" s="9" t="n"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="H3" s="53" t="inlineStr"/>
+      <c r="I3" s="53" t="inlineStr"/>
+      <c r="J3" s="53" t="inlineStr"/>
+      <c r="K3" s="53" t="inlineStr"/>
+      <c r="L3" s="53" t="inlineStr">
         <is>
           <t>5770L</t>
         </is>
       </c>
-      <c r="M3" s="9" t="n">
+      <c r="M3" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="72" t="inlineStr">
+      <c r="N3" s="53" t="inlineStr">
         <is>
           <t>AHC-X36</t>
         </is>
       </c>
-      <c r="P3" s="9" t="n"/>
+      <c r="O3" s="53" t="inlineStr"/>
+      <c r="P3" s="53" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="83" t="n">
+      <c r="A4" s="53" t="n">
         <v>8817000581</v>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="53" t="inlineStr">
         <is>
           <t>AHC-X46</t>
         </is>
       </c>
-      <c r="C4" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="83" t="n"/>
-      <c r="E4" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" s="83" t="n"/>
-      <c r="I4" s="84">
-        <f>SUM(C4:H4)</f>
-        <v/>
-      </c>
-      <c r="J4" s="62" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="C4" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="53" t="inlineStr"/>
+      <c r="E4" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="53" t="inlineStr"/>
+      <c r="I4" s="53" t="inlineStr"/>
+      <c r="J4" s="53" t="inlineStr"/>
+      <c r="K4" s="53" t="inlineStr"/>
+      <c r="L4" s="53" t="inlineStr">
         <is>
           <t>6770L</t>
         </is>
       </c>
-      <c r="N4" s="72" t="inlineStr">
+      <c r="M4" s="53" t="inlineStr"/>
+      <c r="N4" s="53" t="inlineStr">
         <is>
           <t>AHC-X46</t>
         </is>
       </c>
-      <c r="P4" s="9" t="n"/>
+      <c r="O4" s="53" t="inlineStr"/>
+      <c r="P4" s="53" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="83" t="n">
+      <c r="A5" s="53" t="n">
         <v>8817000399</v>
       </c>
-      <c r="B5" s="72" t="inlineStr">
+      <c r="B5" s="53" t="inlineStr">
         <is>
           <t>HEP2150</t>
         </is>
       </c>
-      <c r="C5" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="83" t="n"/>
-      <c r="E5" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="83" t="n"/>
-      <c r="I5" s="83">
-        <f>SUM(C5:G5)</f>
-        <v/>
-      </c>
-      <c r="J5" s="61" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
+      <c r="C5" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="53" t="inlineStr"/>
+      <c r="E5" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="53" t="inlineStr"/>
+      <c r="I5" s="53" t="inlineStr"/>
+      <c r="J5" s="53" t="inlineStr"/>
+      <c r="K5" s="53" t="inlineStr"/>
+      <c r="L5" s="53" t="inlineStr"/>
+      <c r="M5" s="53" t="inlineStr"/>
+      <c r="N5" s="53" t="inlineStr"/>
+      <c r="O5" s="53" t="inlineStr"/>
+      <c r="P5" s="53" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="83" t="n">
+      <c r="A6" s="53" t="n">
         <v>8817000551</v>
       </c>
-      <c r="B6" s="72" t="inlineStr">
+      <c r="B6" s="53" t="inlineStr">
         <is>
           <t>HSA-X20</t>
         </is>
       </c>
-      <c r="C6" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="83" t="n"/>
-      <c r="E6" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="83" t="n"/>
-      <c r="I6" s="84">
-        <f>SUM(C6:G6)</f>
-        <v/>
-      </c>
-      <c r="J6" s="63" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="C6" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="53" t="inlineStr"/>
+      <c r="E6" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="53" t="inlineStr"/>
+      <c r="I6" s="53" t="inlineStr"/>
+      <c r="J6" s="53" t="inlineStr"/>
+      <c r="K6" s="53" t="inlineStr"/>
+      <c r="L6" s="53" t="inlineStr">
         <is>
           <t>3810L</t>
         </is>
       </c>
-      <c r="M6" s="50" t="n">
+      <c r="M6" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="N6" s="72" t="inlineStr">
+      <c r="N6" s="53" t="inlineStr">
         <is>
           <t>HSA-X20</t>
         </is>
@@ -15205,93 +12623,89 @@
           <t>12/10 庫存已扣</t>
         </is>
       </c>
-      <c r="P6" s="9" t="n">
+      <c r="P6" s="53" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="83" t="n">
+      <c r="A7" s="53" t="n">
         <v>8817000552</v>
       </c>
-      <c r="B7" s="72" t="inlineStr">
+      <c r="B7" s="53" t="inlineStr">
         <is>
           <t>HSA-X20EAY</t>
         </is>
       </c>
-      <c r="C7" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="83" t="n"/>
-      <c r="E7" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="83" t="n"/>
-      <c r="I7" s="84">
-        <f>SUM(C7:G7)</f>
-        <v/>
-      </c>
-      <c r="J7" s="63" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="C7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="53" t="inlineStr"/>
+      <c r="E7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="53" t="inlineStr"/>
+      <c r="I7" s="53" t="inlineStr"/>
+      <c r="J7" s="53" t="inlineStr"/>
+      <c r="K7" s="53" t="inlineStr"/>
+      <c r="L7" s="53" t="inlineStr">
         <is>
           <t>4150L</t>
         </is>
       </c>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="72" t="inlineStr">
+      <c r="M7" s="53" t="inlineStr"/>
+      <c r="N7" s="53" t="inlineStr">
         <is>
           <t>HSA-X20EAY</t>
         </is>
       </c>
-      <c r="O7" s="53" t="n"/>
-      <c r="P7" s="9" t="n">
+      <c r="O7" s="53" t="inlineStr"/>
+      <c r="P7" s="53" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="83" t="n">
+      <c r="A8" s="53" t="n">
         <v>8817000491</v>
       </c>
-      <c r="B8" s="72" t="inlineStr">
+      <c r="B8" s="53" t="inlineStr">
         <is>
           <t>HSA-X23</t>
         </is>
       </c>
-      <c r="C8" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="83" t="n"/>
-      <c r="E8" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="83" t="n">
+      <c r="C8" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="53" t="inlineStr"/>
+      <c r="E8" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="83" t="n"/>
-      <c r="I8" s="84">
-        <f>SUM(C8:G8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="63" t="n"/>
-      <c r="K8" s="45" t="n"/>
-      <c r="L8" s="45" t="inlineStr">
+      <c r="H8" s="53" t="inlineStr"/>
+      <c r="I8" s="53" t="n">
+        <v>6</v>
+      </c>
+      <c r="J8" s="53" t="inlineStr"/>
+      <c r="K8" s="53" t="inlineStr"/>
+      <c r="L8" s="53" t="inlineStr">
         <is>
           <t>3960L</t>
         </is>
       </c>
-      <c r="M8" s="8" t="n">
+      <c r="M8" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="N8" s="72" t="inlineStr">
+      <c r="N8" s="53" t="inlineStr">
         <is>
           <t>HSA-X23</t>
         </is>
@@ -15301,47 +12715,47 @@
           <t>M6:16HR，M5:22HR</t>
         </is>
       </c>
-      <c r="P8" s="61" t="n"/>
+      <c r="P8" s="53" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="83" t="n">
+      <c r="A9" s="53" t="n">
         <v>8817000517</v>
       </c>
-      <c r="B9" s="54" t="inlineStr">
+      <c r="B9" s="53" t="inlineStr">
         <is>
           <t>HSA-X23EAY</t>
         </is>
       </c>
-      <c r="C9" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="83" t="n">
+      <c r="C9" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="H9" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="84" t="n">
+      <c r="D9" s="53" t="inlineStr"/>
+      <c r="E9" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="J9" s="63" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="12" t="inlineStr">
+      <c r="H9" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="53" t="inlineStr"/>
+      <c r="K9" s="53" t="inlineStr"/>
+      <c r="L9" s="53" t="inlineStr">
         <is>
           <t>4650L</t>
         </is>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="54" t="inlineStr">
+      <c r="N9" s="53" t="inlineStr">
         <is>
           <t>HSA-X23EAY</t>
         </is>
@@ -15351,500 +12765,382 @@
           <t>M6:18HR，M5:37HR</t>
         </is>
       </c>
+      <c r="P9" s="53" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="83" t="n">
+      <c r="A10" s="53" t="n">
         <v>8817000483</v>
       </c>
-      <c r="B10" s="72" t="inlineStr">
+      <c r="B10" s="53" t="inlineStr">
         <is>
           <t>HSA-X27</t>
         </is>
       </c>
-      <c r="C10" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="83" t="n"/>
-      <c r="E10" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="83" t="n">
+      <c r="C10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="53" t="inlineStr"/>
+      <c r="E10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="83" t="n"/>
-      <c r="I10" s="84">
-        <f>SUM(C10:G10)</f>
-        <v/>
-      </c>
-      <c r="J10" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
+      <c r="H10" s="53" t="inlineStr"/>
+      <c r="I10" s="53" t="inlineStr"/>
+      <c r="J10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="53" t="inlineStr">
         <is>
           <t>台典成品*1,4600L</t>
         </is>
       </c>
-      <c r="M10" s="45" t="n">
+      <c r="M10" s="53" t="n">
         <v>6</v>
       </c>
-      <c r="N10" s="72" t="inlineStr">
+      <c r="N10" s="53" t="inlineStr">
         <is>
           <t>HSA-X27</t>
         </is>
       </c>
-      <c r="O10" s="53" t="n"/>
-      <c r="P10" s="9" t="n"/>
+      <c r="O10" s="53" t="inlineStr"/>
+      <c r="P10" s="53" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="83" t="n">
+      <c r="A11" s="53" t="n">
         <v>8817000518</v>
       </c>
-      <c r="B11" s="86" t="inlineStr">
+      <c r="B11" s="53" t="inlineStr">
         <is>
           <t>HSA-X27EAY</t>
         </is>
       </c>
-      <c r="C11" s="85" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="85" t="n"/>
-      <c r="E11" s="85" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="85" t="n">
+      <c r="C11" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="53" t="inlineStr"/>
+      <c r="E11" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="85" t="n">
+      <c r="G11" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="83" t="n"/>
-      <c r="I11" s="84" t="n">
+      <c r="H11" s="53" t="inlineStr"/>
+      <c r="I11" s="53" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" s="53" t="inlineStr"/>
+      <c r="K11" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="53" t="inlineStr">
+        <is>
+          <t>5150-5130</t>
+        </is>
+      </c>
+      <c r="M11" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X27EAY</t>
+        </is>
+      </c>
+      <c r="O11" s="53" t="inlineStr">
+        <is>
+          <t>M6-1*3 OK</t>
+        </is>
+      </c>
+      <c r="P11" s="53" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="53" t="n">
+        <v>8817000547</v>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X32</t>
+        </is>
+      </c>
+      <c r="C12" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="53" t="inlineStr"/>
+      <c r="E12" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="53" t="inlineStr"/>
+      <c r="I12" s="53" t="inlineStr"/>
+      <c r="J12" s="53" t="inlineStr"/>
+      <c r="K12" s="53" t="inlineStr"/>
+      <c r="L12" s="53" t="inlineStr">
+        <is>
+          <t>5050L</t>
+        </is>
+      </c>
+      <c r="M12" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X32</t>
+        </is>
+      </c>
+      <c r="O12" s="53" t="inlineStr"/>
+      <c r="P12" s="53" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="53" t="n">
+        <v>8817000548</v>
+      </c>
+      <c r="B13" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X32EAY</t>
+        </is>
+      </c>
+      <c r="C13" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="53" t="inlineStr"/>
+      <c r="E13" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="53" t="inlineStr"/>
+      <c r="I13" s="53" t="inlineStr"/>
+      <c r="J13" s="53" t="inlineStr"/>
+      <c r="K13" s="53" t="inlineStr"/>
+      <c r="L13" s="53" t="inlineStr">
+        <is>
+          <t>5600L</t>
+        </is>
+      </c>
+      <c r="M13" s="53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X32EAY</t>
+        </is>
+      </c>
+      <c r="O13" s="53" t="inlineStr"/>
+      <c r="P13" s="53" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="53" t="n">
+        <v>8817000568</v>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X36EAY</t>
+        </is>
+      </c>
+      <c r="C14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="53" t="inlineStr"/>
+      <c r="E14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="53" t="inlineStr"/>
+      <c r="I14" s="53" t="inlineStr"/>
+      <c r="J14" s="53" t="inlineStr"/>
+      <c r="K14" s="53" t="inlineStr"/>
+      <c r="L14" s="53" t="inlineStr">
+        <is>
+          <t>5950L</t>
+        </is>
+      </c>
+      <c r="M14" s="53" t="inlineStr"/>
+      <c r="N14" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X36EAY</t>
+        </is>
+      </c>
+      <c r="O14" s="53" t="inlineStr">
+        <is>
+          <t>隆升借放*4-有入帳</t>
+        </is>
+      </c>
+      <c r="P14" s="53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="53" t="n">
+        <v>8817000485</v>
+      </c>
+      <c r="B15" s="53" t="inlineStr">
+        <is>
+          <t>HSA-X36</t>
+        </is>
+      </c>
+      <c r="C15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="53" t="inlineStr"/>
+      <c r="E15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="J11" s="64" t="n"/>
-      <c r="K11" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>5150-5130</t>
-        </is>
-      </c>
-      <c r="M11" s="43" t="n">
-        <v>2</v>
-      </c>
-      <c r="N11" s="54" t="inlineStr">
-        <is>
-          <t>HSA-X27EAY</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr">
-        <is>
-          <t>M6-1*3 OK</t>
-        </is>
-      </c>
-      <c r="P11" s="9" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="83" t="n">
-        <v>8817000547</v>
-      </c>
-      <c r="B12" s="72" t="inlineStr">
-        <is>
-          <t>HSA-X32</t>
-        </is>
-      </c>
-      <c r="C12" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="83" t="n"/>
-      <c r="E12" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="83" t="n">
-        <v>2</v>
-      </c>
-      <c r="H12" s="83" t="n"/>
-      <c r="I12" s="84">
-        <f>SUM(C12:G12)</f>
-        <v/>
-      </c>
-      <c r="J12" s="63" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="inlineStr">
-        <is>
-          <t>5050L</t>
-        </is>
-      </c>
-      <c r="M12" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" s="72" t="inlineStr">
-        <is>
-          <t>HSA-X32</t>
-        </is>
-      </c>
-      <c r="O12" s="53" t="n"/>
-      <c r="P12" s="9" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="83" t="n">
-        <v>8817000548</v>
-      </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>HSA-X32EAY</t>
-        </is>
-      </c>
-      <c r="C13" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="83" t="n"/>
-      <c r="E13" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="83" t="n"/>
-      <c r="I13" s="84">
-        <f>SUM(C13:G13)</f>
-        <v/>
-      </c>
-      <c r="J13" s="63" t="n"/>
-      <c r="K13" s="9" t="n"/>
-      <c r="L13" s="9" t="inlineStr">
+      <c r="H15" s="53" t="inlineStr"/>
+      <c r="I15" s="53" t="inlineStr"/>
+      <c r="J15" s="53" t="inlineStr"/>
+      <c r="K15" s="53" t="inlineStr">
+        <is>
+          <t>`</t>
+        </is>
+      </c>
+      <c r="L15" s="53" t="inlineStr">
         <is>
           <t>5600L</t>
         </is>
       </c>
-      <c r="M13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N13" s="72" t="inlineStr">
-        <is>
-          <t>HSA-X32EAY</t>
-        </is>
-      </c>
-      <c r="O13" s="53" t="n"/>
-      <c r="P13" s="9" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="83" t="n">
-        <v>8817000568</v>
-      </c>
-      <c r="B14" s="54" t="inlineStr">
-        <is>
-          <t>HSA-X36EAY</t>
-        </is>
-      </c>
-      <c r="C14" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="83" t="n"/>
-      <c r="E14" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="84">
-        <f>SUM(C14:G14)</f>
-        <v/>
-      </c>
-      <c r="J14" s="63" t="n"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>5950L</t>
-        </is>
-      </c>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="54" t="inlineStr">
-        <is>
-          <t>HSA-X36EAY</t>
-        </is>
-      </c>
-      <c r="O14" s="53" t="inlineStr">
-        <is>
-          <t>隆升借放*4-有入帳</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="83" t="n">
-        <v>8817000485</v>
-      </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="M15" s="53" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" s="53" t="inlineStr">
         <is>
           <t>HSA-X36</t>
         </is>
       </c>
-      <c r="C15" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="83" t="n"/>
-      <c r="E15" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="83" t="n">
-        <v>5</v>
-      </c>
-      <c r="H15" s="83" t="n"/>
-      <c r="I15" s="84">
-        <f>SUM(C15:G15)</f>
-        <v/>
-      </c>
-      <c r="J15" s="63" t="n"/>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>`</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>5600L</t>
-        </is>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" s="54" t="inlineStr">
-        <is>
-          <t>HSA-X36</t>
-        </is>
-      </c>
-      <c r="O15" s="53" t="n"/>
-      <c r="P15" s="9" t="n"/>
+      <c r="O15" s="53" t="inlineStr"/>
+      <c r="P15" s="53" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="83" t="n">
+      <c r="A16" s="53" t="n">
         <v>8817000635</v>
       </c>
-      <c r="B16" s="54" t="inlineStr">
+      <c r="B16" s="53" t="inlineStr">
         <is>
           <t>TGV-106</t>
         </is>
       </c>
-      <c r="C16" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="83" t="n"/>
-      <c r="E16" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="83" t="n"/>
-      <c r="I16" s="83">
-        <f>SUM(C16:G16)</f>
-        <v/>
-      </c>
-      <c r="J16" s="61" t="n"/>
-      <c r="L16" s="53" t="n"/>
-      <c r="M16" s="53" t="n"/>
-      <c r="N16" s="53" t="n"/>
-      <c r="O16" s="53" t="n"/>
-      <c r="P16" s="53" t="n"/>
+      <c r="C16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="53" t="inlineStr"/>
+      <c r="E16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="53" t="inlineStr"/>
+      <c r="I16" s="53" t="inlineStr"/>
+      <c r="J16" s="53" t="inlineStr"/>
+      <c r="K16" s="53" t="inlineStr"/>
+      <c r="L16" s="53" t="inlineStr"/>
+      <c r="M16" s="53" t="inlineStr"/>
+      <c r="N16" s="53" t="inlineStr"/>
+      <c r="O16" s="53" t="inlineStr"/>
+      <c r="P16" s="53" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="83" t="n">
+      <c r="A17" s="53" t="n">
         <v>8817000441</v>
       </c>
-      <c r="B17" s="54" t="inlineStr">
+      <c r="B17" s="53" t="inlineStr">
         <is>
           <t>HSA-X23_NEO</t>
         </is>
       </c>
-      <c r="C17" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="83" t="n"/>
-      <c r="I17" s="83">
-        <f>SUM(C17:G17)</f>
-        <v/>
-      </c>
-      <c r="J17" s="61" t="n"/>
-      <c r="L17" s="53" t="n"/>
-      <c r="M17" s="53" t="n"/>
-      <c r="N17" s="53" t="n"/>
-      <c r="O17" s="53" t="n"/>
-      <c r="P17" s="53" t="n"/>
+      <c r="C17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="53" t="inlineStr"/>
+      <c r="I17" s="53" t="inlineStr"/>
+      <c r="J17" s="53" t="inlineStr"/>
+      <c r="K17" s="53" t="inlineStr"/>
+      <c r="L17" s="53" t="inlineStr"/>
+      <c r="M17" s="53" t="inlineStr"/>
+      <c r="N17" s="53" t="inlineStr"/>
+      <c r="O17" s="53" t="inlineStr"/>
+      <c r="P17" s="53" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="83" t="n">
+      <c r="A18" s="53" t="n">
         <v>8817000650</v>
       </c>
-      <c r="B18" s="54" t="inlineStr">
+      <c r="B18" s="53" t="inlineStr">
         <is>
           <t>HSA-X20_NEO</t>
         </is>
       </c>
-      <c r="C18" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="54" t="n"/>
-      <c r="I18" s="83">
-        <f>SUM(C18:G18)</f>
-        <v/>
-      </c>
-      <c r="J18" s="61" t="n"/>
-      <c r="L18" s="53" t="n"/>
-      <c r="M18" s="53" t="n"/>
-      <c r="N18" s="53" t="n"/>
-      <c r="O18" s="53" t="n"/>
-      <c r="P18" s="53" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="83" t="n"/>
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="54" t="n"/>
-      <c r="H19" s="54" t="n"/>
-      <c r="I19" s="54" t="n"/>
-      <c r="J19" s="53" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="83" t="n"/>
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="54" t="n"/>
-      <c r="G20" s="54" t="n"/>
-      <c r="H20" s="54" t="n"/>
-      <c r="I20" s="54" t="n"/>
-      <c r="J20" s="53" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="83" t="n"/>
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-      <c r="H21" s="54" t="n"/>
-      <c r="I21" s="54" t="n"/>
-      <c r="J21" s="53" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="83" t="n"/>
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-      <c r="H22" s="54" t="n"/>
-      <c r="I22" s="54" t="n"/>
-      <c r="J22" s="53" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="83" t="n"/>
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-      <c r="H23" s="54" t="n"/>
-      <c r="I23" s="54" t="n"/>
-      <c r="J23" s="53" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="87" t="n"/>
-      <c r="B24" s="87" t="n"/>
-      <c r="C24" s="87" t="n"/>
-      <c r="D24" s="87" t="n"/>
-      <c r="E24" s="87" t="n"/>
-      <c r="F24" s="87" t="n"/>
-      <c r="G24" s="87" t="n"/>
-      <c r="H24" s="87" t="n"/>
-      <c r="I24" s="87" t="n"/>
-      <c r="J24" s="53" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="53" t="n"/>
-      <c r="B25" s="53" t="n"/>
-      <c r="C25" s="53" t="n"/>
-      <c r="D25" s="53" t="n"/>
-      <c r="E25" s="53" t="n"/>
-      <c r="F25" s="53" t="n"/>
-      <c r="G25" s="53" t="n"/>
-      <c r="H25" s="53" t="n"/>
-      <c r="I25" s="53" t="n"/>
-      <c r="J25" s="53" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="53" t="n"/>
-      <c r="B26" s="53" t="n"/>
-      <c r="C26" s="53" t="n"/>
-      <c r="D26" s="53" t="n"/>
-      <c r="E26" s="53" t="n"/>
-      <c r="F26" s="53" t="n"/>
-      <c r="G26" s="53" t="n"/>
-      <c r="H26" s="53" t="n"/>
-      <c r="I26" s="53" t="n"/>
-      <c r="J26" s="53" t="n"/>
+      <c r="C18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="53" t="inlineStr"/>
+      <c r="I18" s="53" t="inlineStr"/>
+      <c r="J18" s="53" t="inlineStr"/>
+      <c r="K18" s="53" t="inlineStr"/>
+      <c r="L18" s="53" t="inlineStr"/>
+      <c r="M18" s="53" t="inlineStr"/>
+      <c r="N18" s="53" t="inlineStr"/>
+      <c r="O18" s="53" t="inlineStr"/>
+      <c r="P18" s="53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -15934,13 +13230,13 @@
         </is>
       </c>
       <c r="C2" s="53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D2" s="53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2" s="53" t="n">
         <v>0</v>
@@ -16020,10 +13316,10 @@
         <v>0</v>
       </c>
       <c r="D5" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="53" t="n">
         <v>4</v>
-      </c>
-      <c r="E5" s="53" t="n">
-        <v>0</v>
       </c>
       <c r="F5" s="53" t="n">
         <v>0</v>
@@ -16104,7 +13400,7 @@
         </is>
       </c>
       <c r="C8" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="53" t="n">
         <v>0</v>
@@ -16116,7 +13412,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="53" t="inlineStr"/>
       <c r="I8" s="53" t="inlineStr"/>
@@ -16144,10 +13440,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H9" s="53" t="n">
         <v>0</v>

--- a/鑄件盤點資料.xlsx
+++ b/鑄件盤點資料.xlsx
@@ -8654,13 +8654,13 @@
         <v>0</v>
       </c>
       <c r="D2" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="47" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="47" t="inlineStr"/>
       <c r="H2" s="47" t="n">
@@ -9019,7 +9019,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="47" t="inlineStr"/>
       <c r="H13" s="47" t="n">
@@ -9329,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" s="47" t="n">
         <v>0</v>
@@ -9362,20 +9362,20 @@
         </is>
       </c>
       <c r="C23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="D23" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="47" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="47" t="inlineStr"/>
       <c r="H23" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" s="47" t="inlineStr"/>
       <c r="J23" s="47" t="inlineStr"/>
@@ -9438,20 +9438,20 @@
         </is>
       </c>
       <c r="C25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="D25" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="F25" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G25" s="47" t="inlineStr"/>
       <c r="H25" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="47" t="inlineStr"/>
       <c r="J25" s="47" t="inlineStr"/>
@@ -9628,13 +9628,13 @@
         <v>0</v>
       </c>
       <c r="D30" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="E30" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="G30" s="47" t="inlineStr"/>
       <c r="H30" s="47" t="n">
@@ -9700,7 +9700,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" s="47" t="n">
         <v>0</v>
@@ -9733,7 +9733,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="47" t="n">
         <v>0</v>
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="C48" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="D48" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="F48" s="47" t="n">
         <v>0</v>
@@ -10246,10 +10246,10 @@
         </is>
       </c>
       <c r="C49" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="D49" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="E49" s="47" t="n">
         <v>0</v>
@@ -10312,7 +10312,7 @@
         </is>
       </c>
       <c r="C51" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="47" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="47" t="inlineStr"/>
       <c r="H51" s="47" t="n">
@@ -10353,10 +10353,10 @@
         <v>0</v>
       </c>
       <c r="E52" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="F52" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="G52" s="47" t="inlineStr"/>
       <c r="H52" s="47" t="n">
@@ -10737,7 +10737,7 @@
     </row>
     <row r="64">
       <c r="A64" s="47" t="n">
-        <v>8810000964</v>
+        <v>8810000957</v>
       </c>
       <c r="B64" s="47" t="inlineStr">
         <is>
@@ -10745,20 +10745,20 @@
         </is>
       </c>
       <c r="C64" s="47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D64" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" s="47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F64" s="47" t="n">
         <v>0</v>
       </c>
       <c r="G64" s="47" t="inlineStr"/>
       <c r="H64" s="47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I64" s="47" t="inlineStr"/>
       <c r="J64" s="47" t="inlineStr"/>
@@ -10809,13 +10809,13 @@
         </is>
       </c>
       <c r="C66" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E66" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F66" s="47" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H6" s="47" t="n">
         <v>1</v>
@@ -11449,12 +11449,18 @@
       <c r="E8" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="47" t="inlineStr"/>
-      <c r="G8" s="47" t="inlineStr"/>
+      <c r="F8" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="H8" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="47" t="inlineStr"/>
+      <c r="I8" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" s="47" t="inlineStr"/>
       <c r="K8" s="47" t="inlineStr"/>
       <c r="L8" s="47" t="n">
@@ -11613,7 +11619,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="47" t="n">
         <v>0</v>
@@ -11676,7 +11682,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E14" s="47" t="n">
         <v>0</v>
@@ -11962,12 +11968,18 @@
       <c r="E21" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="47" t="inlineStr"/>
-      <c r="G21" s="47" t="inlineStr"/>
+      <c r="F21" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="47" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="47" t="inlineStr"/>
+      <c r="I21" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="J21" s="47" t="inlineStr"/>
       <c r="K21" s="47" t="inlineStr"/>
       <c r="L21" s="47" t="inlineStr"/>
@@ -12121,7 +12133,7 @@
         </is>
       </c>
       <c r="C26" s="47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="47" t="n">
         <v>0</v>
@@ -12133,7 +12145,7 @@
         <v>0</v>
       </c>
       <c r="G26" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="47" t="n">
         <v>1</v>
@@ -12244,18 +12256,20 @@
         <v>0</v>
       </c>
       <c r="E29" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="47" t="n">
-        <v>0</v>
-      </c>
       <c r="H29" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="47" t="inlineStr"/>
+      <c r="I29" s="47" t="n">
+        <v>3</v>
+      </c>
       <c r="J29" s="47" t="n">
         <v>3</v>
       </c>
@@ -12639,7 +12653,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E39" s="47" t="n">
         <v>0</v>
@@ -12653,7 +12667,9 @@
       <c r="H39" s="47" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="47" t="inlineStr"/>
+      <c r="I39" s="47" t="n">
+        <v>0</v>
+      </c>
       <c r="J39" s="47" t="n">
         <v>1</v>
       </c>
@@ -12796,7 +12812,7 @@
         </is>
       </c>
       <c r="C43" s="47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D43" s="47" t="n">
         <v>0</v>
@@ -12808,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="G43" s="47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" s="47" t="n">
         <v>0</v>
@@ -13064,13 +13080,13 @@
       </c>
       <c r="D4" s="47" t="inlineStr"/>
       <c r="E4" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="47" t="n">
         <v>1</v>
-      </c>
-      <c r="F4" s="47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" s="47" t="n">
-        <v>0</v>
       </c>
       <c r="H4" s="47" t="inlineStr"/>
       <c r="I4" s="47" t="n">
@@ -13184,7 +13200,7 @@
         </is>
       </c>
       <c r="C8" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="47" t="inlineStr"/>
       <c r="E8" s="47" t="n">
@@ -13197,7 +13213,9 @@
         <v>0</v>
       </c>
       <c r="H8" s="47" t="inlineStr"/>
-      <c r="I8" s="47" t="inlineStr"/>
+      <c r="I8" s="47" t="n">
+        <v>1</v>
+      </c>
       <c r="J8" s="47" t="inlineStr"/>
       <c r="K8" s="47" t="inlineStr"/>
       <c r="L8" s="47" t="inlineStr">
@@ -13284,7 +13302,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" s="47" t="inlineStr"/>
       <c r="I10" s="47" t="n">
@@ -13428,11 +13446,11 @@
         <v>0</v>
       </c>
       <c r="G13" s="47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="47" t="inlineStr"/>
       <c r="I13" s="47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13" s="47" t="inlineStr"/>
       <c r="K13" s="47" t="n">
@@ -13481,7 +13499,9 @@
         <v>2</v>
       </c>
       <c r="H14" s="47" t="inlineStr"/>
-      <c r="I14" s="47" t="inlineStr"/>
+      <c r="I14" s="47" t="n">
+        <v>2</v>
+      </c>
       <c r="J14" s="47" t="inlineStr"/>
       <c r="K14" s="47" t="inlineStr"/>
       <c r="L14" s="47" t="inlineStr">
@@ -13816,458 +13836,466 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="47" t="inlineStr"/>
+      <c r="B2" s="47" t="inlineStr">
         <is>
           <t>5BC-4300</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
+      <c r="D2" s="47" t="inlineStr"/>
+      <c r="E2" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="F2" s="47" t="inlineStr"/>
+      <c r="G2" s="47" t="inlineStr"/>
+      <c r="H2" s="47" t="inlineStr"/>
+      <c r="I2" s="47" t="inlineStr"/>
+      <c r="J2" s="47" t="inlineStr"/>
+      <c r="K2" s="47" t="inlineStr"/>
+      <c r="L2" s="47" t="inlineStr"/>
+      <c r="M2" s="47" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
+      <c r="A3" s="47" t="inlineStr"/>
+      <c r="B3" s="47" t="inlineStr">
         <is>
           <t>HEP2150-1720</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="C3" s="47" t="inlineStr"/>
+      <c r="D3" s="47" t="inlineStr"/>
+      <c r="E3" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="F3" s="47" t="inlineStr"/>
+      <c r="G3" s="47" t="inlineStr"/>
+      <c r="H3" s="47" t="inlineStr"/>
+      <c r="I3" s="47" t="inlineStr"/>
+      <c r="J3" s="47" t="inlineStr"/>
+      <c r="K3" s="47" t="inlineStr"/>
+      <c r="L3" s="47" t="inlineStr"/>
+      <c r="M3" s="47" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr"/>
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>HEP2150-1620</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="E4" s="47" t="inlineStr"/>
+      <c r="F4" s="47" t="inlineStr"/>
+      <c r="G4" s="47" t="inlineStr"/>
+      <c r="H4" s="47" t="inlineStr"/>
+      <c r="I4" s="47" t="inlineStr"/>
+      <c r="J4" s="47" t="inlineStr"/>
+      <c r="K4" s="47" t="inlineStr"/>
+      <c r="L4" s="47" t="inlineStr"/>
+      <c r="M4" s="47" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr">
+      <c r="A5" s="47" t="inlineStr"/>
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>HSA4265</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="D5" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="47" t="inlineStr"/>
+      <c r="G5" s="47" t="inlineStr"/>
+      <c r="H5" s="47" t="inlineStr"/>
+      <c r="I5" s="47" t="inlineStr"/>
+      <c r="J5" s="47" t="inlineStr"/>
+      <c r="K5" s="47" t="inlineStr"/>
+      <c r="L5" s="47" t="inlineStr"/>
+      <c r="M5" s="47" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="n">
-        <v>8811001091</v>
-      </c>
-      <c r="B6" t="inlineStr">
+      <c r="A6" s="47" t="inlineStr">
+        <is>
+          <t>8811001113</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>LG-800</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>8</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="C6" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" s="47" t="inlineStr"/>
+      <c r="I6" s="47" t="inlineStr"/>
+      <c r="J6" s="47" t="inlineStr"/>
+      <c r="K6" s="47" t="inlineStr"/>
+      <c r="L6" s="47" t="inlineStr"/>
+      <c r="M6" s="47" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="47" t="n">
         <v>8811001273</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>LG-1370</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="C7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="47" t="inlineStr"/>
+      <c r="H7" s="47" t="inlineStr"/>
+      <c r="I7" s="47" t="inlineStr"/>
+      <c r="J7" s="47" t="inlineStr"/>
+      <c r="K7" s="47" t="inlineStr"/>
+      <c r="L7" s="47" t="inlineStr"/>
+      <c r="M7" s="47" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="47" t="n">
         <v>8811001013</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>MVP-860</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="C8" s="47" t="inlineStr"/>
+      <c r="D8" s="47" t="inlineStr"/>
+      <c r="E8" s="47" t="inlineStr"/>
+      <c r="F8" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="47" t="inlineStr"/>
+      <c r="H8" s="47" t="inlineStr"/>
+      <c r="I8" s="47" t="inlineStr"/>
+      <c r="J8" s="47" t="inlineStr"/>
+      <c r="K8" s="47" t="inlineStr"/>
+      <c r="L8" s="47" t="inlineStr"/>
+      <c r="M8" s="47" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="47" t="n">
         <v>8811001077</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>MVP-860+200H</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="47" t="inlineStr"/>
+      <c r="I9" s="47" t="inlineStr"/>
+      <c r="J9" s="47" t="inlineStr"/>
+      <c r="K9" s="47" t="inlineStr"/>
+      <c r="L9" s="47" t="inlineStr"/>
+      <c r="M9" s="47" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="47" t="n">
+        <v>8811001393</v>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>MVP-11</t>
+        </is>
+      </c>
+      <c r="C10" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="47" t="inlineStr"/>
+      <c r="I10" s="47" t="inlineStr"/>
+      <c r="J10" s="47" t="inlineStr"/>
+      <c r="K10" s="47" t="inlineStr"/>
+      <c r="L10" s="47" t="inlineStr"/>
+      <c r="M10" s="47" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="47" t="n">
+        <v>8811001536</v>
+      </c>
+      <c r="B11" s="47" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="C11" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="47" t="inlineStr"/>
+      <c r="H11" s="47" t="inlineStr"/>
+      <c r="I11" s="47" t="inlineStr"/>
+      <c r="J11" s="47" t="inlineStr"/>
+      <c r="K11" s="47" t="inlineStr"/>
+      <c r="L11" s="47" t="inlineStr"/>
+      <c r="M11" s="47" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="47" t="n">
+        <v>8811001338</v>
+      </c>
+      <c r="B12" s="47" t="inlineStr">
+        <is>
+          <t>S-PLUS 8</t>
+        </is>
+      </c>
+      <c r="C12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="47" t="inlineStr"/>
+      <c r="F12" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="47" t="inlineStr"/>
+      <c r="H12" s="47" t="inlineStr"/>
+      <c r="I12" s="47" t="inlineStr"/>
+      <c r="J12" s="47" t="inlineStr"/>
+      <c r="K12" s="47" t="inlineStr"/>
+      <c r="L12" s="47" t="inlineStr"/>
+      <c r="M12" s="47" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="47" t="n">
+        <v>8811001526</v>
+      </c>
+      <c r="B13" s="47" t="inlineStr">
+        <is>
+          <t>S8</t>
+        </is>
+      </c>
+      <c r="C13" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="47" t="inlineStr"/>
+      <c r="I13" s="47" t="inlineStr"/>
+      <c r="J13" s="47" t="inlineStr"/>
+      <c r="K13" s="47" t="inlineStr"/>
+      <c r="L13" s="47" t="inlineStr"/>
+      <c r="M13" s="47" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="47" t="n">
+        <v>8811001616</v>
+      </c>
+      <c r="B14" s="47" t="inlineStr">
+        <is>
+          <t>LG-1370-NEO</t>
+        </is>
+      </c>
+      <c r="C14" s="47" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>8811001393</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MVP-11</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>8811001536</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>8811001338</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>S-PLUS 8</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>8811001526</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>S8</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
+      <c r="D14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="47" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="47" t="inlineStr"/>
+      <c r="J14" s="47" t="inlineStr"/>
+      <c r="K14" s="47" t="inlineStr">
+        <is>
+          <t>M1:14.5HR</t>
+        </is>
+      </c>
+      <c r="L14" s="47" t="inlineStr">
+        <is>
+          <t>M2:7.5HR</t>
+        </is>
+      </c>
+      <c r="M14" s="47" t="inlineStr">
+        <is>
+          <t>M7:2.HR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="47" t="n">
+        <v>8811001625</v>
+      </c>
+      <c r="B15" s="47" t="inlineStr">
+        <is>
+          <t>LG-1370-NEO+200H</t>
+        </is>
+      </c>
+      <c r="C15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="47" t="inlineStr"/>
+      <c r="J15" s="47" t="inlineStr"/>
+      <c r="K15" s="47" t="inlineStr"/>
+      <c r="L15" s="47" t="inlineStr"/>
+      <c r="M15" s="47" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="47" t="n">
+        <v>8811001619</v>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>LG-1000-NEO</t>
+        </is>
+      </c>
+      <c r="C16" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
+      <c r="D16" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="47" t="inlineStr"/>
+      <c r="H16" s="47" t="inlineStr"/>
+      <c r="I16" s="47" t="inlineStr"/>
+      <c r="J16" s="47" t="inlineStr"/>
+      <c r="K16" s="47" t="inlineStr"/>
+      <c r="L16" s="47" t="inlineStr"/>
+      <c r="M16" s="47" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="47" t="n">
+        <v>8811001623</v>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>LG-1000-NEO+200H</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>8811001616</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>LG-1370-NEO</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>M1:14.5HR</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>M2:7.5HR</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>M7:2.HR</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>8811001625</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>LG-1370-NEO+200H</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>8811001619</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>LG-1000-NEO</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>8811001623</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>LG-1000-NEO+200H</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
+      <c r="D17" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="47" t="inlineStr"/>
+      <c r="H17" s="47" t="inlineStr"/>
+      <c r="I17" s="47" t="inlineStr"/>
+      <c r="J17" s="47" t="inlineStr"/>
+      <c r="K17" s="47" t="inlineStr"/>
+      <c r="L17" s="47" t="inlineStr"/>
+      <c r="M17" s="47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
